--- a/server/src/data/西班牙语单词本-动词.xlsx
+++ b/server/src/data/西班牙语单词本-动词.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ydy\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\我的项目\业务mvp\vocabulario-espanol\server\src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60963974-68E4-4EF4-ADAF-6E3F6164445A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F5F1E6A-5A03-4D91-B6D3-E2F9686575DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="31200" yWindow="1875" windowWidth="21600" windowHeight="11235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="33675" yWindow="1200" windowWidth="21600" windowHeight="11235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="动词表" sheetId="2" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="726" uniqueCount="726">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="732" uniqueCount="718">
   <si>
     <t>原形</t>
   </si>
@@ -51,13 +51,13 @@
     <t>发现</t>
   </si>
   <si>
-    <t>descubre（三单）</t>
-  </si>
-  <si>
-    <t>他在旧书里发现一首情诗</t>
-  </si>
-  <si>
-    <t>El descubre un poema de amor en un libro viejo</t>
+    <t>descubre（三单） | 第一人称(yo): descubro | 第二人称(tú): descubres | 第三人称(él/ella/usted): descubre</t>
+  </si>
+  <si>
+    <t>他在旧书里发现一首情诗。</t>
+  </si>
+  <si>
+    <t>El descubre un poema de amor en un libro viejo.</t>
   </si>
   <si>
     <t>搭配：descubrir un secreto发现秘密；及物动词，直接加宾语</t>
@@ -69,13 +69,13 @@
     <t>分析</t>
   </si>
   <si>
-    <t>analiza（三单）</t>
-  </si>
-  <si>
-    <t>分析着泛黄的笔迹</t>
-  </si>
-  <si>
-    <t>analiza la escritura descolorida</t>
+    <t>analiza（三单） | 第一人称(yo): analizo | 第二人称(tú): analizas | 第三人称(él/ella/usted): analiza</t>
+  </si>
+  <si>
+    <t>他分析着泛黄的笔迹。</t>
+  </si>
+  <si>
+    <t>Él analiza la escritura descolorida.</t>
   </si>
   <si>
     <t>-ar变位动词；搭配：analizar datos分析数据</t>
@@ -87,13 +87,13 @@
     <t>发展</t>
   </si>
   <si>
-    <t>desarrollar（原形）</t>
-  </si>
-  <si>
-    <t>决定把故事发展成短篇小说</t>
-  </si>
-  <si>
-    <t>decide desarrollar la historia en un relato corto</t>
+    <t>desarrollar（原形） | 第一人称(yo): desarrollo | 第二人称(tú): desarrollas | 第三人称(él/ella/usted): desarrolla</t>
+  </si>
+  <si>
+    <t>他决定把故事发展成短篇小说。</t>
+  </si>
+  <si>
+    <t>Él decide desarrollar la historia en un relato corto.</t>
   </si>
   <si>
     <t>搭配：desarrollar un proyecto发展项目；自复desarrollarse发展</t>
@@ -105,13 +105,13 @@
     <t>要求</t>
   </si>
   <si>
-    <t>exige（三单）</t>
-  </si>
-  <si>
-    <t>艺术不强求解释</t>
-  </si>
-  <si>
-    <t>El arte no exige explicación</t>
+    <t>exige（三单） | 第一人称(yo): exigo | 第二人称(tú): exiges | 第三人称(él/ella/usted): exige</t>
+  </si>
+  <si>
+    <t>他艺术不强求解释。</t>
+  </si>
+  <si>
+    <t>El arte no exige explicación.</t>
   </si>
   <si>
     <t>搭配：exigir algo a alguien向某人要求某事；需加前置词a</t>
@@ -123,13 +123,13 @@
     <t>调查</t>
   </si>
   <si>
-    <t>investigar（原形）</t>
-  </si>
-  <si>
-    <t>邀请人们体察情感，探寻感受的新天地</t>
-  </si>
-  <si>
-    <t>invita a investigar la emoción</t>
+    <t>investigar（原形） | 第一人称(yo): investigo | 第二人称(tú): investigas | 第三人称(él/ella/usted): investiga</t>
+  </si>
+  <si>
+    <t>邀请人们体察情感，探寻感受的新天地。</t>
+  </si>
+  <si>
+    <t>Él invita a investigar la emoción.</t>
   </si>
   <si>
     <t>搭配：investigar un caso调查案件；及物动词</t>
@@ -141,13 +141,13 @@
     <t>探索</t>
   </si>
   <si>
-    <t>explorar（原形）</t>
-  </si>
-  <si>
-    <t>探寻感受的新天地</t>
-  </si>
-  <si>
-    <t>explorar nuevos paisajes del sentir</t>
+    <t>explorar（原形） | 第一人称(yo): exploro | 第二人称(tú): exploras | 第三人称(él/ella/usted): explora</t>
+  </si>
+  <si>
+    <t>他探寻感受的新天地。</t>
+  </si>
+  <si>
+    <t>Él explorar nuevos paisajes del sentir.</t>
   </si>
   <si>
     <t>搭配：explorar un lugar探索某地；及物动词</t>
@@ -159,13 +159,13 @@
     <t>监督</t>
   </si>
   <si>
-    <t>supervisa（三单）</t>
-  </si>
-  <si>
-    <t>黄昏监督白昼的退场</t>
-  </si>
-  <si>
-    <t>El crepusculo supervisa la retirada del día</t>
+    <t>supervisa（三单） | 第一人称(yo): superviso | 第二人称(tú): supervisas | 第三人称(él/ella/usted): supervisa</t>
+  </si>
+  <si>
+    <t>他黄昏监督白昼的退场。</t>
+  </si>
+  <si>
+    <t>El crepusculo supervisa la retirada del día.</t>
   </si>
   <si>
     <t>搭配：supervisar un trabajo监督工作；及物动词</t>
@@ -177,13 +177,13 @@
     <t>调节</t>
   </si>
   <si>
-    <t>regulan（三复）</t>
-  </si>
-  <si>
-    <t>星辰调节夜色的浓度</t>
-  </si>
-  <si>
-    <t>las estrellas regulan la densidad de la noche</t>
+    <t>regulan（三复） | 第一人称(yo): regulo | 第二人称(tú): regulas | 第三人称(él/ella/usted): regula</t>
+  </si>
+  <si>
+    <t>他星辰调节夜色的浓度。</t>
+  </si>
+  <si>
+    <t>Él las estrellas regulan la densidad de la noche.</t>
   </si>
   <si>
     <t>搭配：regular la temperatura调节温度；及物动词</t>
@@ -195,13 +195,13 @@
     <t>禁止</t>
   </si>
   <si>
-    <t>prohíbe（三单）</t>
-  </si>
-  <si>
-    <t>天空从不禁止任何一缕光穿越黑暗</t>
-  </si>
-  <si>
-    <t>el cielo nunca prohibe que ningún rayo de luz atraviese la oscuridad</t>
+    <t>prohíbe（三单） | 第一人称(yo): prohibo | 第二人称(tú): prohibes | 第三人称(él/ella/usted): prohibe</t>
+  </si>
+  <si>
+    <t>他天空从不禁止任何一缕光穿越黑暗。</t>
+  </si>
+  <si>
+    <t>El ciElo nunca prohibe que ningún rayo de luz atraviese la oscuridad.</t>
   </si>
   <si>
     <t>搭配：prohibir algo a alguien禁止某人某事；变位特殊：yo prohíbo</t>
@@ -213,13 +213,13 @@
     <t>祝贺</t>
   </si>
   <si>
-    <t>felicita（三单）</t>
-  </si>
-  <si>
-    <t>时间祝贺每一次日出</t>
-  </si>
-  <si>
-    <t>EI tiempo felicita cada amanecer</t>
+    <t>felicita（三单） | 第一人称(yo): felicito | 第二人称(tú): felicitas | 第三人称(él/ella/usted): felicita</t>
+  </si>
+  <si>
+    <t>时间祝贺每一次日出。</t>
+  </si>
+  <si>
+    <t>El tiempo felicita cada amanecer.</t>
   </si>
   <si>
     <t>搭配：felicitar a alguien por algo为某事祝贺某人；需加前置词a</t>
@@ -231,13 +231,13 @@
     <t>控制</t>
   </si>
   <si>
-    <t>controla（三单）</t>
-  </si>
-  <si>
-    <t>从不过分控制光的轨迹</t>
-  </si>
-  <si>
-    <t>nunca controla en exceso la trayectoria de la luz</t>
+    <t>controla（三单） | 第一人称(yo): controlo | 第二人称(tú): controlas | 第三人称(él/ella/usted): controla</t>
+  </si>
+  <si>
+    <t>他从不过分控制光的轨迹。</t>
+  </si>
+  <si>
+    <t>Él nunca controla en exceso la trayectoria de la luz.</t>
   </si>
   <si>
     <t>搭配：controlar el tiempo控制时间；及物动词</t>
@@ -249,13 +249,13 @@
     <t>管理</t>
   </si>
   <si>
-    <t>administra（三单）</t>
-  </si>
-  <si>
-    <t>安静地管理着昼夜的秩序</t>
-  </si>
-  <si>
-    <t>solo administra en silencio el orden del dia y la noche</t>
+    <t>administra（三单） | 第一人称(yo): administro | 第二人称(tú): administras | 第三人称(él/ella/usted): administra</t>
+  </si>
+  <si>
+    <t>他安静地管理着昼夜的秩序。</t>
+  </si>
+  <si>
+    <t>Él solo administra en silencio el orden del dia y la noche.</t>
   </si>
   <si>
     <t>搭配：administrar una empresa管理公司；及物动词</t>
@@ -267,13 +267,13 @@
     <t>陪伴</t>
   </si>
   <si>
-    <t>acompaña（三单）</t>
-  </si>
-  <si>
-    <t>月光陪伴失眠的人</t>
-  </si>
-  <si>
-    <t>La luna acompana a quienes no duermen</t>
+    <t>acompaña（三单） | 第一人称(yo): acompano | 第二人称(tú): acompanas | 第三人称(él/ella/usted): acompana</t>
+  </si>
+  <si>
+    <t>他月光陪伴失眠的人。</t>
+  </si>
+  <si>
+    <t>La luna acompana a quienes no duermen.</t>
   </si>
   <si>
     <t>搭配：acompañar a alguien陪伴某人；需加前置词a</t>
@@ -285,13 +285,13 @@
     <t>介绍</t>
   </si>
   <si>
-    <t>presenta（三单）</t>
-  </si>
-  <si>
-    <t>晨露介绍新的一天</t>
-  </si>
-  <si>
-    <t>el rocio matinal presenta un nuevo día</t>
+    <t>presenta（三单） | 第一人称(yo): presento | 第二人称(tú): presentas | 第三人称(él/ella/usted): presenta</t>
+  </si>
+  <si>
+    <t>他晨露介绍新的一天。</t>
+  </si>
+  <si>
+    <t>El rocio matinal presenta un nuevo día.</t>
   </si>
   <si>
     <t>搭配：presentar a alguien介绍某人；及物动词</t>
@@ -303,13 +303,13 @@
     <t>推荐</t>
   </si>
   <si>
-    <t>recomienda（三单）</t>
-  </si>
-  <si>
-    <t>春风推荐散步的路线</t>
-  </si>
-  <si>
-    <t>la brisa primaveral recomienda rutas para caminar</t>
+    <t>recomienda（三单） | 第一人称(yo): recomendo | 第二人称(tú): recomendas | 第三人称(él/ella/usted): recomenda</t>
+  </si>
+  <si>
+    <t>他春风推荐散步的路线。</t>
+  </si>
+  <si>
+    <t>Él la brisa primaveral recomienda rutas para caminar.</t>
   </si>
   <si>
     <t>搭配：recomendar algo a alguien向某人推荐某物；变位特殊：yo recomiendo</t>
@@ -321,13 +321,13 @@
     <t>使高兴</t>
   </si>
   <si>
-    <t>alegra（三单）</t>
-  </si>
-  <si>
-    <t>初雪让整条街的孩子都高兴起来</t>
-  </si>
-  <si>
-    <t>La primera nevada alegra a todos los ninos de la calle</t>
+    <t>alegra（三单） | 第一人称(yo): alegro | 第二人称(tú): alegras | 第三人称(él/ella/usted): alegra</t>
+  </si>
+  <si>
+    <t>他初雪让整条街的孩子都高兴起来。</t>
+  </si>
+  <si>
+    <t>La primera nevada alegra a todos los ninos de la calle.</t>
   </si>
   <si>
     <t>使役动词；搭配：alegrar el corazón使人心喜</t>
@@ -339,13 +339,13 @@
     <t>使平静</t>
   </si>
   <si>
-    <t>tranquiliza（三单）</t>
-  </si>
-  <si>
-    <t>热巧克力的香气使人平静</t>
-  </si>
-  <si>
-    <t>el aroma del chocolate caliente tranquiliza</t>
+    <t>tranquiliza（三单） | 第一人称(yo): tranquilizo | 第二人称(tú): tranquilizas | 第三人称(él/ella/usted): tranquiliza</t>
+  </si>
+  <si>
+    <t>他热巧克力的香气使人平静。</t>
+  </si>
+  <si>
+    <t>El aroma dEl chocolate caliente tranquiliza.</t>
   </si>
   <si>
     <t>使役动词；搭配：tranquilizar los nervios平复紧张</t>
@@ -357,13 +357,13 @@
     <t>邀请</t>
   </si>
   <si>
-    <t>invita（三单）</t>
-  </si>
-  <si>
-    <t>咖啡馆的灯光温柔地邀请着每个过路人</t>
-  </si>
-  <si>
-    <t>la luz de la cafetería invita con suavidad a cada transeúnte</t>
+    <t>invita（三单） | 第一人称(yo): invito | 第二人称(tú): invitas | 第三人称(él/ella/usted): invita</t>
+  </si>
+  <si>
+    <t>他咖啡馆的灯光温柔地邀请着每个过路人。</t>
+  </si>
+  <si>
+    <t>Él la luz de la cafetería invita con suavidad a cada transeúnte.</t>
   </si>
   <si>
     <t>搭配：invitar a alguien a hacer algo邀请某人做某事；需加前置词a</t>
@@ -375,13 +375,13 @@
     <t>惊吓</t>
   </si>
   <si>
-    <t>asusta（三单）</t>
-  </si>
-  <si>
-    <t>雨声惊吓到流浪猫</t>
-  </si>
-  <si>
-    <t>La lluvia asusta a los gatos callejeros</t>
+    <t>asusta（三单） | 第一人称(yo): asusto | 第二人称(tú): asustas | 第三人称(él/ella/usted): asusta</t>
+  </si>
+  <si>
+    <t>他雨声惊吓到流浪猫。</t>
+  </si>
+  <si>
+    <t>La lluvia asusta a los gatos callejeros.</t>
   </si>
   <si>
     <t>使役动词；搭配：asustar a alguien惊吓某人</t>
@@ -393,13 +393,13 @@
     <t>使惊讶</t>
   </si>
   <si>
-    <t>sorprende（三单）</t>
-  </si>
-  <si>
-    <t>彩虹使孩子们惊喜</t>
-  </si>
-  <si>
-    <t>el arcoiris sorprende a los ninos</t>
+    <t>sorprende（三单） | 第一人称(yo): sorprendo | 第二人称(tú): sorprendes | 第三人称(él/ella/usted): sorprende</t>
+  </si>
+  <si>
+    <t>他彩虹使孩子们惊喜。</t>
+  </si>
+  <si>
+    <t>El arcoiris sorprende a los ninos.</t>
   </si>
   <si>
     <t>使役动词；搭配：sorprender a alguien使某人惊讶</t>
@@ -411,13 +411,13 @@
     <t>使担心</t>
   </si>
   <si>
-    <t>preocupa（三单）</t>
-  </si>
-  <si>
-    <t>未归的亲人使人担忧</t>
-  </si>
-  <si>
-    <t>el familiar que no regresa preocupa</t>
+    <t>preocupa（三单） | 第一人称(yo): preocupo | 第二人称(tú): preocupas | 第三人称(él/ella/usted): preocupa</t>
+  </si>
+  <si>
+    <t>他未归的亲人使人担忧。</t>
+  </si>
+  <si>
+    <t>El familiar que no regresa preocupa.</t>
   </si>
   <si>
     <t>使役动词；搭配：preocupar a alguien使某人担心</t>
@@ -429,13 +429,13 @@
     <t>指导</t>
   </si>
   <si>
-    <t>dirige（三单）</t>
-  </si>
-  <si>
-    <t>人生这场考试无人指导</t>
-  </si>
-  <si>
-    <t>En el examen de la vida nadie te dirige</t>
+    <t>dirige（三单） | 第一人称(yo): dirigo | 第二人称(tú): diriges | 第三人称(él/ella/usted): dirige</t>
+  </si>
+  <si>
+    <t>人生这场考试无人指导。</t>
+  </si>
+  <si>
+    <t>Él En el examen de la vida nadie te dirige.</t>
   </si>
   <si>
     <t>搭配：dirigir a alguien指导某人；变位特殊：yo dirijo</t>
@@ -447,31 +447,22 @@
     <t>选择</t>
   </si>
   <si>
-    <t>elige（三单）</t>
-  </si>
-  <si>
-    <t>我们必须自己选择答案</t>
-  </si>
-  <si>
-    <t>debes elegir tus propias respuestas</t>
+    <t>elige（三单） | 第一人称(yo): elego | 第二人称(tú): eleges | 第三人称(él/ella/usted): elege</t>
+  </si>
+  <si>
+    <t>我们必须自己选择答案。</t>
+  </si>
+  <si>
+    <t>Él debes elegir tus propias respuestas.</t>
   </si>
   <si>
     <t>变位特殊：yo elijo；搭配：elegir algo选择某物</t>
   </si>
   <si>
-    <t>Exigir</t>
-  </si>
-  <si>
-    <t>要求</t>
-  </si>
-  <si>
-    <t>exige（三单）</t>
-  </si>
-  <si>
-    <t>时间总会要求我们交卷</t>
-  </si>
-  <si>
-    <t>el tiempo siempre exige que entregues la hoja</t>
+    <t>时间总会要求我们交卷。</t>
+  </si>
+  <si>
+    <t>El tiempo siempre exige que entregues la hoja.</t>
   </si>
   <si>
     <t>搭配：exigir que + 虚拟式；需加前置词a</t>
@@ -483,13 +474,13 @@
     <t>完成</t>
   </si>
   <si>
-    <t>completa（三单）</t>
-  </si>
-  <si>
-    <t>河流以入海完成其旅程</t>
-  </si>
-  <si>
-    <t>EI rio completa su viaje desembocando en el mar</t>
+    <t>completa（三单） | 第一人称(yo): completo | 第二人称(tú): completas | 第三人称(él/ella/usted): completa</t>
+  </si>
+  <si>
+    <t>他河流以入海完成其旅程。</t>
+  </si>
+  <si>
+    <t>El rio completa su viaje desembocando en el mar.</t>
   </si>
   <si>
     <t>搭配：completar una tarea完成任务；及物动词</t>
@@ -501,13 +492,13 @@
     <t>使适应/改编</t>
   </si>
   <si>
-    <t>adapta（三单）</t>
-  </si>
-  <si>
-    <t>懂得将自己适应每一道河岸的曲线</t>
-  </si>
-  <si>
-    <t>sabe adaptarse a cada curva de la orilla</t>
+    <t>adapta（三单） | 第一人称(yo): adapto | 第二人称(tú): adaptas | 第三人称(él/ella/usted): adapta</t>
+  </si>
+  <si>
+    <t>他懂得将自己适应每一道河岸的曲线。</t>
+  </si>
+  <si>
+    <t>Él sabe adaptarse a cada curva de la orilla.</t>
   </si>
   <si>
     <t>自复动词adaptarse a适应；搭配：adaptar una obra改编作品</t>
@@ -519,13 +510,13 @@
     <t>解决</t>
   </si>
   <si>
-    <t>resuelve（三单）</t>
-  </si>
-  <si>
-    <t>最终在溶解与交融中解决归处的命题</t>
-  </si>
-  <si>
-    <t>resolviendo al fin en disolución y fusión la cuestion del regreso</t>
+    <t>resuelve（三单） | 第一人称(yo): resolvo | 第二人称(tú): resolves | 第三人称(él/ella/usted): resolve</t>
+  </si>
+  <si>
+    <t>他最终在溶解与交融中解决归处的命题。</t>
+  </si>
+  <si>
+    <t>Él resolviendo al fin en disolución y fusión la cuestion del regreso.</t>
   </si>
   <si>
     <t>变位特殊：yo resuelvo；搭配：resolver un problema解决问题</t>
@@ -537,13 +528,13 @@
     <t>使用</t>
   </si>
   <si>
-    <t>utiliza（三单）</t>
-  </si>
-  <si>
-    <t>她使用传统方法制作陶器</t>
-  </si>
-  <si>
-    <t>Ella utiliza méetodos tradicionales para hacer cerámica</t>
+    <t>utiliza（三单） | 第一人称(yo): utilizo | 第二人称(tú): utilizas | 第三人称(él/ella/usted): utiliza</t>
+  </si>
+  <si>
+    <t>她使用传统方法制作陶器。</t>
+  </si>
+  <si>
+    <t>Ella utiliza méetodos tradicionales para hacer cerámica.</t>
   </si>
   <si>
     <t>搭配：utilizar algo使用某物；及物动词</t>
@@ -555,13 +546,13 @@
     <t>运行</t>
   </si>
   <si>
-    <t>funciona（三单）</t>
-  </si>
-  <si>
-    <t>工作室的拉坯机运行时会发出熟悉的嗡嗡声</t>
-  </si>
-  <si>
-    <t>el torno del taller funciona con un zumbido familiar</t>
+    <t>funciona（三单） | 第一人称(yo): funciono | 第二人称(tú): funcionas | 第三人称(él/ella/usted): funciona</t>
+  </si>
+  <si>
+    <t>他工作室的拉坯机运行时会发出熟悉的嗡嗡声。</t>
+  </si>
+  <si>
+    <t>El torno dEl taller funciona con un zumbido familiar.</t>
   </si>
   <si>
     <t>不及物动词；搭配：funcionar bien运行良好</t>
@@ -573,13 +564,13 @@
     <t>改进</t>
   </si>
   <si>
-    <t>mejora（三单）</t>
-  </si>
-  <si>
-    <t>每件作品都在尝试改进釉料的色彩层次</t>
-  </si>
-  <si>
-    <t>cada pieza intenta mejorar los matices del esmalte</t>
+    <t>mejora（三单） | 第一人称(yo): mejoro | 第二人称(tú): mejoras | 第三人称(él/ella/usted): mejora</t>
+  </si>
+  <si>
+    <t>他每件作品都在尝试改进釉料的色彩层次。</t>
+  </si>
+  <si>
+    <t>Él cada pieza intenta mejorar los matices del esmalte.</t>
   </si>
   <si>
     <t>搭配：mejorar la calidad改进质量；及物动词</t>
@@ -591,13 +582,13 @@
     <t>结束</t>
   </si>
   <si>
-    <t>concluye（三单）</t>
-  </si>
-  <si>
-    <t>秋天以金黄结束盛夏的篇章</t>
-  </si>
-  <si>
-    <t>El otono concluye el capitulo del verano con dorados</t>
+    <t>concluye（三单） | 第一人称(yo): concluo | 第二人称(tú): conclues | 第三人称(él/ella/usted): conclue</t>
+  </si>
+  <si>
+    <t>他秋天以金黄结束盛夏的篇章。</t>
+  </si>
+  <si>
+    <t>El otono concluye el capitulo del verano con dorados.</t>
   </si>
   <si>
     <t>-uir变位动词；搭配：concluir una reunión结束会议</t>
@@ -609,13 +600,13 @@
     <t>分配</t>
   </si>
   <si>
-    <t>distribuye（三单）</t>
-  </si>
-  <si>
-    <t>将果实分配给等待的双手</t>
-  </si>
-  <si>
-    <t>distribuye los frutos a las manos que esperan</t>
+    <t>distribuye（三单） | 第一人称(yo): distribuo | 第二人称(tú): distribues | 第三人称(él/ella/usted): distribue</t>
+  </si>
+  <si>
+    <t>他将果实分配给等待的双手。</t>
+  </si>
+  <si>
+    <t>Él distribuye los frutos a las manos que esperan.</t>
   </si>
   <si>
     <t>搭配：distribuir algo a alguien分配某物给某人；及物动词</t>
@@ -627,13 +618,13 @@
     <t>应用</t>
   </si>
   <si>
-    <t>aplica（三单）</t>
-  </si>
-  <si>
-    <t>并把这份丰饶应用于寒冬的准备</t>
-  </si>
-  <si>
-    <t>aplica esta abundancia en la preparación para el invierno</t>
+    <t>aplica（三单） | 第一人称(yo): aplico | 第二人称(tú): aplicas | 第三人称(él/ella/usted): aplica</t>
+  </si>
+  <si>
+    <t>他并把这份丰饶应用于寒冬的准备。</t>
+  </si>
+  <si>
+    <t>Él aplica esta abundancia en la preparación para el invierno.</t>
   </si>
   <si>
     <t>搭配：aplicar algo a algo把某物应用于某处；及物动词</t>
@@ -645,13 +636,13 @@
     <t>建造</t>
   </si>
   <si>
-    <t>construye（三单）</t>
-  </si>
-  <si>
-    <t>诗人用词语建造意象的城堡</t>
-  </si>
-  <si>
-    <t>El poeta construye castillos de imagenes con palabras</t>
+    <t>construye（三单） | 第一人称(yo): construyo | 第二人称(tú): construyes | 第三人称(él/ella/usted): construye</t>
+  </si>
+  <si>
+    <t>他诗人用词语建造意象的城堡。</t>
+  </si>
+  <si>
+    <t>El poeta construye castillos de imagenes con palabras.</t>
   </si>
   <si>
     <t>变位特殊：yo construyo；搭配：construir un edificio建造建筑</t>
@@ -663,13 +654,13 @@
     <t>破坏</t>
   </si>
   <si>
-    <t>destruye（三单）</t>
-  </si>
-  <si>
-    <t>现实用时间摧毁幻想的城墙</t>
-  </si>
-  <si>
-    <t>la realidad destruye murallas de ilusión con el tiempo</t>
+    <t>destruye（三单） | 第一人称(yo): destruyo | 第二人称(tú): destruyes | 第三人称(él/ella/usted): destruye</t>
+  </si>
+  <si>
+    <t>现实用时间摧毁幻想的城墙。</t>
+  </si>
+  <si>
+    <t>Él la realidad destruye murallas de ilusión con el tiempo.</t>
   </si>
   <si>
     <t>变位特殊：yo destruyo；搭配：destruir algo破坏某物</t>
@@ -681,13 +672,13 @@
     <t>影响</t>
   </si>
   <si>
-    <t>influye（三单）</t>
-  </si>
-  <si>
-    <t>而美永恒地影响着人类的感知</t>
-  </si>
-  <si>
-    <t>la belleza eternamente influye en la percepción humana</t>
+    <t>influye（三单） | 第一人称(yo): influo | 第二人称(tú): influes | 第三人称(él/ella/usted): influe</t>
+  </si>
+  <si>
+    <t>他而美永恒地影响着人类的感知。</t>
+  </si>
+  <si>
+    <t>Él la belleza eternamente influye en la percepción humana.</t>
   </si>
   <si>
     <t>搭配：influir en algo影响某事；需加前置词en</t>
@@ -699,13 +690,13 @@
     <t>挠刮</t>
   </si>
   <si>
-    <t>rascarle（原形+与格）</t>
-  </si>
-  <si>
-    <t>让我挠它的肚皮</t>
-  </si>
-  <si>
-    <t>me deja rascarle la pancita</t>
+    <t>rascarle（原形+与格） | 第一人称(yo): rasco | 第二人称(tú): rascas | 第三人称(él/ella/usted): rasca</t>
+  </si>
+  <si>
+    <t>让我挠它的肚皮。</t>
+  </si>
+  <si>
+    <t>Él me deja rascarle la pancita.</t>
   </si>
   <si>
     <t>搭配：rascar la cabeza挠头；及物动词</t>
@@ -717,13 +708,13 @@
     <t>拥抱</t>
   </si>
   <si>
-    <t>abraza（三单）</t>
-  </si>
-  <si>
-    <t>然后它用爪子抱住我</t>
-  </si>
-  <si>
-    <t>Después me abraza con las patas</t>
+    <t>abraza（三单） | 第一人称(yo): abrazo | 第二人称(tú): abrazas | 第三人称(él/ella/usted): abraza</t>
+  </si>
+  <si>
+    <t>然后它用爪子抱住我。</t>
+  </si>
+  <si>
+    <t>Él Después me abraza con las patas.</t>
   </si>
   <si>
     <t>搭配：abrazar a alguien拥抱某人；需加前置词a</t>
@@ -735,13 +726,13 @@
     <t>亲吻</t>
   </si>
   <si>
-    <t>besa（三单）</t>
-  </si>
-  <si>
-    <t>用粗糙的舌头亲我的鼻子</t>
-  </si>
-  <si>
-    <t>me besa la nariz con su lengua áspera</t>
+    <t>besa（三单） | 第一人称(yo): beso | 第二人称(tú): besas | 第三人称(él/ella/usted): besa</t>
+  </si>
+  <si>
+    <t>用粗糙的舌头亲我的鼻子。</t>
+  </si>
+  <si>
+    <t>Él me besa la nariz con su lengua áspera.</t>
   </si>
   <si>
     <t>搭配：besar a alguien亲吻某人；需加前置词a</t>
@@ -753,13 +744,13 @@
     <t>触摸</t>
   </si>
   <si>
-    <t>toca（三单）</t>
-  </si>
-  <si>
-    <t>我奶奶每次见到我都会触摸我的脸</t>
-  </si>
-  <si>
-    <t>Mi abuela siempre me toca la cara cuando me ve</t>
+    <t>toca（三单） | 第一人称(yo): toco | 第二人称(tú): tocas | 第三人称(él/ella/usted): toca</t>
+  </si>
+  <si>
+    <t>我奶奶每次见到我都会触摸我的脸。</t>
+  </si>
+  <si>
+    <t>Él Mi abuela siempre me toca la cara cuando me ve.</t>
   </si>
   <si>
     <t>搭配：tocar algo触摸某物；及物动词</t>
@@ -771,13 +762,13 @@
     <t>抚摸</t>
   </si>
   <si>
-    <t>acaricia（三单）</t>
-  </si>
-  <si>
-    <t>她用布满皱纹的手抚摸它</t>
-  </si>
-  <si>
-    <t>Me la acaricia con la mano arrugada</t>
+    <t>acaricia（三单） | 第一人称(yo): acaricio | 第二人称(tú): acaricias | 第三人称(él/ella/usted): acaricia</t>
+  </si>
+  <si>
+    <t>她用布满皱纹的手抚摸它。</t>
+  </si>
+  <si>
+    <t>Él Me la acaricia con la mano arrugada.</t>
   </si>
   <si>
     <t>搭配：acariciar a alguien抚摸某人；需加前置词a</t>
@@ -789,13 +780,13 @@
     <t>掐</t>
   </si>
   <si>
-    <t>pellizca（三单）</t>
-  </si>
-  <si>
-    <t>有时她会掐一下我的脸蛋</t>
-  </si>
-  <si>
-    <t>Y a veces me pellizca la mejilla</t>
+    <t>pellizca（三单） | 第一人称(yo): pellizco | 第二人称(tú): pellizcas | 第三人称(él/ella/usted): pellizca</t>
+  </si>
+  <si>
+    <t>有时她会掐一下我的脸蛋。</t>
+  </si>
+  <si>
+    <t>Él Y a veces me pellizca la mejilla.</t>
   </si>
   <si>
     <t>搭配：pellizcar a alguien掐某人；需加前置词a</t>
@@ -807,13 +798,13 @@
     <t>吐</t>
   </si>
   <si>
-    <t>escupir（原形）</t>
-  </si>
-  <si>
-    <t>最后要么咽要么吐</t>
-  </si>
-  <si>
-    <t>al final tragar o escupir</t>
+    <t>escupir（原形） | 第一人称(yo): escupo | 第二人称(tú): escupes | 第三人称(él/ella/usted): escupe</t>
+  </si>
+  <si>
+    <t>他最后要么咽要么吐。</t>
+  </si>
+  <si>
+    <t>Él al final tragar o escupir.</t>
   </si>
   <si>
     <t>不及物/及物动词；搭配：escupir algo吐某物</t>
@@ -825,13 +816,13 @@
     <t>闻</t>
   </si>
   <si>
-    <t>oler（原形）</t>
-  </si>
-  <si>
-    <t>先闻</t>
-  </si>
-  <si>
-    <t>primero oler</t>
+    <t>oler（原形） | 第一人称(yo): olo | 第二人称(tú): oles | 第三人称(él/ella/usted): ole</t>
+  </si>
+  <si>
+    <t>他先闻。</t>
+  </si>
+  <si>
+    <t>Él primero oler.</t>
   </si>
   <si>
     <t>变位特殊：yo huelo；搭配：oler algo闻某物</t>
@@ -843,13 +834,13 @@
     <t>品</t>
   </si>
   <si>
-    <t>saborear（原形）</t>
-  </si>
-  <si>
-    <t>再品</t>
-  </si>
-  <si>
-    <t>luego saborear</t>
+    <t>saborear（原形） | 第一人称(yo): saboreo | 第二人称(tú): saboreas | 第三人称(él/ella/usted): saborea</t>
+  </si>
+  <si>
+    <t>他再品。</t>
+  </si>
+  <si>
+    <t>Él luego saborear.</t>
   </si>
   <si>
     <t>搭配：saborear la comida品尝食物；及物动词</t>
@@ -861,13 +852,13 @@
     <t>咬</t>
   </si>
   <si>
-    <t>muerdo（一单）</t>
-  </si>
-  <si>
-    <t>我想都没想就咬了一口面包</t>
-  </si>
-  <si>
-    <t>le muerdo al pan sin pensar</t>
+    <t>muerdo（一单） | 第一人称(yo): mordo | 第二人称(tú): mordes | 第三人称(él/ella/usted): morde</t>
+  </si>
+  <si>
+    <t>我想都没想就咬了一口面包。</t>
+  </si>
+  <si>
+    <t>Él le muerdo al pan sin pensar.</t>
   </si>
   <si>
     <t>变位特殊：yo muerdo；搭配：morder algo咬某物</t>
@@ -879,13 +870,13 @@
     <t>咀嚼</t>
   </si>
   <si>
-    <t>mastico（一单）</t>
-  </si>
-  <si>
-    <t>飞快地嚼了几口</t>
-  </si>
-  <si>
-    <t>Lo mastico rapido</t>
+    <t>mastico（一单） | 第一人称(yo): mastico | 第二人称(tú): masticas | 第三人称(él/ella/usted): mastica</t>
+  </si>
+  <si>
+    <t>他飞快地嚼了几口。</t>
+  </si>
+  <si>
+    <t>Él Lo mastico rapido.</t>
   </si>
   <si>
     <t>搭配：masticar la comida咀嚼食物；及物动词</t>
@@ -897,13 +888,13 @@
     <t>吞咽</t>
   </si>
   <si>
-    <t>tragó（三单过去式）</t>
-  </si>
-  <si>
-    <t>咽下去，肚子总算不叫了</t>
-  </si>
-  <si>
-    <t>Lo trago y la panza deja de quejarse</t>
+    <t>tragó（三单过去式） | 第一人称(yo): trago | 第二人称(tú): tragas | 第三人称(él/ella/usted): traga</t>
+  </si>
+  <si>
+    <t>他咽下去，肚子总算不叫了。</t>
+  </si>
+  <si>
+    <t>Él Lo trago y la panza deja de quejarse.</t>
   </si>
   <si>
     <t>搭配：tragar algo吞咽某物；及物动词</t>
@@ -915,13 +906,13 @@
     <t>打喷嚏</t>
   </si>
   <si>
-    <t>estornudo（一单）</t>
-  </si>
-  <si>
-    <t>春天一到，我就打喷嚏打个不停</t>
-  </si>
-  <si>
-    <t>no paro de estornudar</t>
+    <t>estornudo（一单） | 第一人称(yo): estornudo | 第二人称(tú): estornudas | 第三人称(él/ella/usted): estornuda</t>
+  </si>
+  <si>
+    <t>春天一到，我就打喷嚏打个不停。</t>
+  </si>
+  <si>
+    <t>Él no paro de estornudar.</t>
   </si>
   <si>
     <t>不及物动词；无变位特殊</t>
@@ -933,13 +924,13 @@
     <t>打哈欠</t>
   </si>
   <si>
-    <t>bostezo（一单）</t>
-  </si>
-  <si>
-    <t>过敏让我老想打哈欠</t>
-  </si>
-  <si>
-    <t>Bostezar me da sueno por la alergia</t>
+    <t>bostezo（一单） | 第一人称(yo): bostezo | 第二人称(tú): bostezas | 第三人称(él/ella/usted): bosteza</t>
+  </si>
+  <si>
+    <t>过敏让我老想打哈欠。</t>
+  </si>
+  <si>
+    <t>Él Bostezar me da sueno por la alergia.</t>
   </si>
   <si>
     <t>不及物动词；搭配：bostezar de sueño困得打哈欠</t>
@@ -951,13 +942,13 @@
     <t>眨眼</t>
   </si>
   <si>
-    <t>parpadeo（一单）</t>
-  </si>
-  <si>
-    <t>我只能靠眨眼来不让眼睛那么难受</t>
-  </si>
-  <si>
-    <t>solo puedo parpadear para que no me lloren los ojos</t>
+    <t>parpadeo（一单） | 第一人称(yo): parpadeo | 第二人称(tú): parpadeas | 第三人称(él/ella/usted): parpadea</t>
+  </si>
+  <si>
+    <t>我只能靠眨眼来不让眼睛那么难受。</t>
+  </si>
+  <si>
+    <t>Él solo puedo parpadear para que no me lloren los ojos.</t>
   </si>
   <si>
     <t>不及物动词；搭配：parpadear rápido快速眨眼</t>
@@ -969,13 +960,13 @@
     <t>呼吸</t>
   </si>
   <si>
-    <t>respiro（一单）</t>
-  </si>
-  <si>
-    <t>跑完步之后，我只能深呼吸</t>
-  </si>
-  <si>
-    <t>solo atino a respirar hondo</t>
+    <t>respiro（一单） | 第一人称(yo): respiro | 第二人称(tú): respiras | 第三人称(él/ella/usted): respira</t>
+  </si>
+  <si>
+    <t>跑完步之后，我只能深呼吸。</t>
+  </si>
+  <si>
+    <t>Él solo atino a respirar hondo.</t>
   </si>
   <si>
     <t>搭配：respirar hondo深呼吸；及物/不及物</t>
@@ -987,13 +978,13 @@
     <t>出汗</t>
   </si>
   <si>
-    <t>sudo（一单）</t>
-  </si>
-  <si>
-    <t>出汗是免不了的</t>
-  </si>
-  <si>
-    <t>Sudar es inevitable</t>
+    <t>sudo（一单） | 第一人称(yo): sudo | 第二人称(tú): sudas | 第三人称(él/ella/usted): suda</t>
+  </si>
+  <si>
+    <t>他出汗是免不了的。</t>
+  </si>
+  <si>
+    <t>Él Sudar es inevitable.</t>
   </si>
   <si>
     <t>不及物动词；搭配：sudar mucho出很多汗</t>
@@ -1005,13 +996,13 @@
     <t>咳嗽</t>
   </si>
   <si>
-    <t>toso（一单）</t>
-  </si>
-  <si>
-    <t>然后会咳嗽几下</t>
-  </si>
-  <si>
-    <t>luego viene toser un poco</t>
+    <t>toso（一单） | 第一人称(yo): toso | 第二人称(tú): toses | 第三人称(él/ella/usted): tose</t>
+  </si>
+  <si>
+    <t>他然后会咳嗽几下。</t>
+  </si>
+  <si>
+    <t>Él luego viene toser un poco.</t>
   </si>
   <si>
     <t>不及物动词；搭配：toser seco干咳</t>
@@ -1023,13 +1014,13 @@
     <t>使惊奇</t>
   </si>
   <si>
-    <t>asombra（三单）</t>
-  </si>
-  <si>
-    <t>一场雨怎么就能改变整个心情，这让我很惊奇</t>
-  </si>
-  <si>
-    <t>Me asombra cómo la lluvia cambia todo el animo</t>
+    <t>asombra（三单） | 第一人称(yo): asombro | 第二人称(tú): asombras | 第三人称(él/ella/usted): asombra</t>
+  </si>
+  <si>
+    <t>一场雨怎么就能改变整个心情，这让我很惊奇。</t>
+  </si>
+  <si>
+    <t>Él Me asombra cómo la lluvia cambia todo el animo.</t>
   </si>
   <si>
     <t>使役动词；搭配：asombrar a alguien使某人惊奇</t>
@@ -1041,13 +1032,13 @@
     <t>安慰</t>
   </si>
   <si>
-    <t>consuela（三单）</t>
-  </si>
-  <si>
-    <t>泥土的湿气味安慰了我</t>
-  </si>
-  <si>
-    <t>Me consuela el olor a tierra mojada</t>
+    <t>consuela（三单） | 第一人称(yo): consolo | 第二人称(tú): consolas | 第三人称(él/ella/usted): consola</t>
+  </si>
+  <si>
+    <t>泥土的湿气味安慰了我。</t>
+  </si>
+  <si>
+    <t>Él Me consuela el olor a tierra mojada.</t>
   </si>
   <si>
     <t>搭配：consolar a alguien安慰某人；需加前置词a</t>
@@ -1059,13 +1050,13 @@
     <t>鼓励</t>
   </si>
   <si>
-    <t>anima（三单）</t>
-  </si>
-  <si>
-    <t>想着明天会出太阳，这鼓励了我</t>
-  </si>
-  <si>
-    <t>Me anima pensar que manana va a salir el sol</t>
+    <t>anima（三单） | 第一人称(yo): animo | 第二人称(tú): animas | 第三人称(él/ella/usted): anima</t>
+  </si>
+  <si>
+    <t>想着明天会出太阳，这鼓励了我。</t>
+  </si>
+  <si>
+    <t>Él Me anima pensar que manana va a salir el sol.</t>
   </si>
   <si>
     <t>搭配：animar a alguien鼓励某人；需加前置词a</t>
@@ -1077,13 +1068,13 @@
     <t>想念</t>
   </si>
   <si>
-    <t>extrano（一单）</t>
-  </si>
-  <si>
-    <t>我想念小时候不用想星期一的星期天</t>
-  </si>
-  <si>
-    <t>Extrano los domingos de la infancia</t>
+    <t>extrano（一单） | 第一人称(yo): extrano | 第二人称(tú): extranas | 第三人称(él/ella/usted): extrana</t>
+  </si>
+  <si>
+    <t>我想念小时候不用想星期一的星期天。</t>
+  </si>
+  <si>
+    <t>Él Extrano los domingos de la infancia.</t>
   </si>
   <si>
     <t>搭配：extranar a alguien想念某人；需加前置词a</t>
@@ -1095,13 +1086,13 @@
     <t>使不悦</t>
   </si>
   <si>
-    <t>disgusta（三单）</t>
-  </si>
-  <si>
-    <t>黄昏时那种焦虑感让我不悦</t>
-  </si>
-  <si>
-    <t>Me disgusta sentir esa ansiedad al atardecer</t>
+    <t>disgusta（三单） | 第一人称(yo): disgusto | 第二人称(tú): disgustas | 第三人称(él/ella/usted): disgusta</t>
+  </si>
+  <si>
+    <t>黄昏时那种焦虑感让我不悦。</t>
+  </si>
+  <si>
+    <t>Él Me disgusta sentir esa ansiedad al atardecer.</t>
   </si>
   <si>
     <t>使役动词；搭配：disgustar a alguien使某人不悦</t>
@@ -1113,13 +1104,13 @@
     <t>使生气</t>
   </si>
   <si>
-    <t>enfada（三单）</t>
-  </si>
-  <si>
-    <t>周末总是结束得那么快，这让我生气</t>
-  </si>
-  <si>
-    <t>Me enfada que el finde termine siempre tan rapido</t>
+    <t>enfada（三单） | 第一人称(yo): enfado | 第二人称(tú): enfadas | 第三人称(él/ella/usted): enfada</t>
+  </si>
+  <si>
+    <t>周末总是结束得那么快，这让我生气。</t>
+  </si>
+  <si>
+    <t>Él Me enfada que el finde termine siempre tan rapido.</t>
   </si>
   <si>
     <t>使役动词；搭配：enfadar a alguien使某人生气</t>
@@ -1131,13 +1122,13 @@
     <t>称重</t>
   </si>
   <si>
-    <t>peso（一单）</t>
-  </si>
-  <si>
-    <t>每天早上我都称一下体重</t>
-  </si>
-  <si>
-    <t>Me peso cada manana</t>
+    <t>peso（一单） | 第一人称(yo): peso | 第二人称(tú): pesas | 第三人称(él/ella/usted): pesa</t>
+  </si>
+  <si>
+    <t>每天早上我都称一下体重。</t>
+  </si>
+  <si>
+    <t>Él Me peso cada manana.</t>
   </si>
   <si>
     <t>自复动词pesarse称重；及物动词pesar某物重</t>
@@ -1149,13 +1140,13 @@
     <t>计算</t>
   </si>
   <si>
-    <t>calculo（一单）</t>
-  </si>
-  <si>
-    <t>算我吃了多少卡路里</t>
-  </si>
-  <si>
-    <t>calculo las calorías que como</t>
+    <t>calculo（一单） | 第一人称(yo): calculo | 第二人称(tú): calculas | 第三人称(él/ella/usted): calcula</t>
+  </si>
+  <si>
+    <t>算我吃了多少卡路里。</t>
+  </si>
+  <si>
+    <t>Él calculo las calorías que como.</t>
   </si>
   <si>
     <t>搭配：calcular algo计算某物；及物动词</t>
@@ -1167,13 +1158,13 @@
     <t>总结</t>
   </si>
   <si>
-    <t>resumo（一单）</t>
-  </si>
-  <si>
-    <t>最后总结：减肥比增肥难多了</t>
-  </si>
-  <si>
-    <t>y resumo que bajar de peso es mas dificil que subir</t>
+    <t>resumo（一单） | 第一人称(yo): resumo | 第二人称(tú): resumes | 第三人称(él/ella/usted): resume</t>
+  </si>
+  <si>
+    <t>他最后总结：减肥比增肥难多了。</t>
+  </si>
+  <si>
+    <t>Él y resumo que bajar de peso es mas dificil que subir.</t>
   </si>
   <si>
     <t>搭配：resumir algo总结某事；及物动词</t>
@@ -1185,13 +1176,13 @@
     <t>比较</t>
   </si>
   <si>
-    <t>comparo（一单）</t>
-  </si>
-  <si>
-    <t>比较摄像头</t>
-  </si>
-  <si>
-    <t>Comparo cámaras</t>
+    <t>comparo（一单） | 第一人称(yo): comparo | 第二人称(tú): comparas | 第三人称(él/ella/usted): compara</t>
+  </si>
+  <si>
+    <t>他比较摄像头。</t>
+  </si>
+  <si>
+    <t>Él Comparo cámaras.</t>
   </si>
   <si>
     <t>搭配：comparar A con B比较A和B；及物动词</t>
@@ -1203,13 +1194,13 @@
     <t>评估</t>
   </si>
   <si>
-    <t>evalúo（一单）</t>
-  </si>
-  <si>
-    <t>评估每个型号的电池</t>
-  </si>
-  <si>
-    <t>evalúo la batería de cada modelo</t>
+    <t>evalúo（一单） | 第一人称(yo): evaluo | 第二人称(tú): evaluas | 第三人称(él/ella/usted): evalua</t>
+  </si>
+  <si>
+    <t>他评估每个型号的电池。</t>
+  </si>
+  <si>
+    <t>Él evalúo la batería de cada modelo.</t>
   </si>
   <si>
     <t>搭配：evaluar algo评估某物；变位特殊：yo evalúo</t>
@@ -1221,13 +1212,13 @@
     <t>测量</t>
   </si>
   <si>
-    <t>mido（一单）</t>
-  </si>
-  <si>
-    <t>量屏幕尺寸</t>
-  </si>
-  <si>
-    <t>mido el tamano de la pantalla</t>
+    <t>mido（一单） | 第一人称(yo): medo | 第二人称(tú): medes | 第三人称(él/ella/usted): mede</t>
+  </si>
+  <si>
+    <t>他量屏幕尺寸。</t>
+  </si>
+  <si>
+    <t>Él mido el tamano de la pantalla.</t>
   </si>
   <si>
     <t>变位特殊：yo mido；搭配：medir algo测量某物</t>
@@ -1239,13 +1230,13 @@
     <t>想象</t>
   </si>
   <si>
-    <t>imagino（一单）</t>
-  </si>
-  <si>
-    <t>我看着一朵云，想象它是一条龙</t>
-  </si>
-  <si>
-    <t>Miro una nube e imagino que es un dragón</t>
+    <t>imagino（一单） | 第一人称(yo): imagino | 第二人称(tú): imaginas | 第三人称(él/ella/usted): imagina</t>
+  </si>
+  <si>
+    <t>我看着一朵云，想象它是一条龙。</t>
+  </si>
+  <si>
+    <t>Él Miro una nube e imagino que es un dragón.</t>
   </si>
   <si>
     <t>搭配：imaginar algo想象某物；及物动词</t>
@@ -1257,13 +1248,13 @@
     <t>假设</t>
   </si>
   <si>
-    <t>supongo（一单）</t>
-  </si>
-  <si>
-    <t>我猜你肯定看到的是别的</t>
-  </si>
-  <si>
-    <t>Tú, en cambio, supongo que ves otra cosa</t>
+    <t>supongo（一单） | 第一人称(yo): supono | 第二人称(tú): supones | 第三人称(él/ella/usted): supone</t>
+  </si>
+  <si>
+    <t>我猜你肯定看到的是别的。</t>
+  </si>
+  <si>
+    <t>Él Tú, en cambio, supongo que ves otra cosa.</t>
   </si>
   <si>
     <t>搭配：suponer algo假设某物；及物动词</t>
@@ -1275,13 +1266,13 @@
     <t>推断</t>
   </si>
   <si>
-    <t>deduco（一单）</t>
-  </si>
-  <si>
-    <t>所以我推断，每个人都是爱怎么看天就怎么看</t>
-  </si>
-  <si>
-    <t>Asi que deduzco que cada uno mira el cielo como le da la gana</t>
+    <t>deduco（一单） | 第一人称(yo): deduco | 第二人称(tú): deduces | 第三人称(él/ella/usted): deduce</t>
+  </si>
+  <si>
+    <t>所以我推断，每个人都是爱怎么看天就怎么看。</t>
+  </si>
+  <si>
+    <t>Él Asi que deduzco que cada uno mira el cielo como le da la gana.</t>
   </si>
   <si>
     <t>变位特殊：yo deduzco；搭配：deducir algo推断某事</t>
@@ -1293,13 +1284,13 @@
     <t>握住</t>
   </si>
   <si>
-    <t>sujetar（原形）</t>
-  </si>
-  <si>
-    <t>我想抓住睡意</t>
-  </si>
-  <si>
-    <t>Quiero sujetar el sueno</t>
+    <t>sujetar（原形） | 第一人称(yo): sujeto | 第二人称(tú): sujetas | 第三人称(él/ella/usted): sujeta</t>
+  </si>
+  <si>
+    <t>我想抓住睡意。</t>
+  </si>
+  <si>
+    <t>Él Quiero sujetar el sueno.</t>
   </si>
   <si>
     <t>搭配：sujetar algo握住某物；及物动词</t>
@@ -1311,13 +1302,13 @@
     <t>松开</t>
   </si>
   <si>
-    <t>suelta（三单）</t>
-  </si>
-  <si>
-    <t>但一闭眼它就溜走了</t>
-  </si>
-  <si>
-    <t>pero se me suelta en cuanto cierro los ojos</t>
+    <t>suelta（三单） | 第一人称(yo): solto | 第二人称(tú): soltas | 第三人称(él/ella/usted): solta</t>
+  </si>
+  <si>
+    <t>但一闭眼它就溜走了。</t>
+  </si>
+  <si>
+    <t>Él pero se me suelta en cuanto cierro los ojos.</t>
   </si>
   <si>
     <t>变位特殊：yo suelto；搭配：soltar algo松开某物</t>
@@ -1329,13 +1320,13 @@
     <t>做梦</t>
   </si>
   <si>
-    <t>sonar（原形）</t>
-  </si>
-  <si>
-    <t>然后我就开始睁着眼睛做梦</t>
-  </si>
-  <si>
-    <t>Entonces empiezo a sonar despierto</t>
+    <t>sonar（原形） | 第一人称(yo): sono | 第二人称(tú): sonas | 第三人称(él/ella/usted): sona</t>
+  </si>
+  <si>
+    <t>然后我就开始睁着眼睛做梦。</t>
+  </si>
+  <si>
+    <t>Él Entonces empiezo a sonar despierto.</t>
   </si>
   <si>
     <t>不及物动词；搭配：sonar con algo梦到某事</t>
@@ -1347,13 +1338,13 @@
     <t>领导</t>
   </si>
   <si>
-    <t>lidera（三单）</t>
-  </si>
-  <si>
-    <t>我家做主的是我妈</t>
-  </si>
-  <si>
-    <t>En mi casa, lidera mi mamá</t>
+    <t>lidera（三单） | 第一人称(yo): lidero | 第二人称(tú): lideras | 第三人称(él/ella/usted): lidera</t>
+  </si>
+  <si>
+    <t>我家做主的是我妈。</t>
+  </si>
+  <si>
+    <t>Él En mi casa, lidera mi mamá.</t>
   </si>
   <si>
     <t>搭配：liderar un equipo领导团队；及物动词</t>
@@ -1365,13 +1356,13 @@
     <t>谈判</t>
   </si>
   <si>
-    <t>negociamos（一单复）</t>
-  </si>
-  <si>
-    <t>度假的事大家商量着来</t>
-  </si>
-  <si>
-    <t>Para decidir las vacaciones, negociamos entre todos</t>
+    <t>negociamos（一单复） | 第一人称(yo): negocio | 第二人称(tú): negocias | 第三人称(él/ella/usted): negocia</t>
+  </si>
+  <si>
+    <t>他度假的事大家商量着来。</t>
+  </si>
+  <si>
+    <t>Él Para decidir las vacaciones, negociamos entre todos.</t>
   </si>
   <si>
     <t>搭配：negociar con alguien和某人谈判；及物动词</t>
@@ -1383,13 +1374,13 @@
     <t>竞争</t>
   </si>
   <si>
-    <t>competimos（一单复）</t>
-  </si>
-  <si>
-    <t>我们不争</t>
-  </si>
-  <si>
-    <t>No competimos</t>
+    <t>competimos（一单复） | 第一人称(yo): competo | 第二人称(tú): competes | 第三人称(él/ella/usted): compete</t>
+  </si>
+  <si>
+    <t>我们不争。</t>
+  </si>
+  <si>
+    <t>Él No competimos.</t>
   </si>
   <si>
     <t>变位特殊：yo compito；搭配：competir con alguien和某人竞争</t>
@@ -1401,13 +1392,13 @@
     <t>服从</t>
   </si>
   <si>
-    <t>obedecer（原形）</t>
-  </si>
-  <si>
-    <t>服从自己的原则比取悦别人更重要</t>
-  </si>
-  <si>
-    <t>Obedecer a tus principios es mas importante que agradar a los demas</t>
+    <t>obedecer（原形） | 第一人称(yo): obedeco | 第二人称(tú): obedeces | 第三人称(él/ella/usted): obedece</t>
+  </si>
+  <si>
+    <t>他服从自己的原则比取悦别人更重要。</t>
+  </si>
+  <si>
+    <t>Él Obedecer a tus principios es mas importante que agradar a los demas.</t>
   </si>
   <si>
     <t>搭配：obedecer a alguien服从某人；需加前置词a</t>
@@ -1419,13 +1410,13 @@
     <t>不服从</t>
   </si>
   <si>
-    <t>desobedecer（原形）</t>
-  </si>
-  <si>
-    <t>不服从不公正的命令，可能是一种勇敢的行为</t>
-  </si>
-  <si>
-    <t>desobedecer una orden injusta puede ser un acto de valentia</t>
+    <t>desobedecer（原形） | 第一人称(yo): desobedeco | 第二人称(tú): desobedeces | 第三人称(él/ella/usted): desobedece</t>
+  </si>
+  <si>
+    <t>他不服从不公正的命令，可能是一种勇敢的行为。</t>
+  </si>
+  <si>
+    <t>Él desobedecer una orden injusta puede ser un acto de valentia.</t>
   </si>
   <si>
     <t>搭配：desobedecer a alguien不服从某人；需加前置词a</t>
@@ -1437,13 +1428,13 @@
     <t>履行/遵守</t>
   </si>
   <si>
-    <t>cumplirla（原形+宾格）</t>
-  </si>
-  <si>
-    <t>承诺就得履行，不管付出什么代价</t>
-  </si>
-  <si>
-    <t>Una promesa hay que cumplirla, cueste lo que cueste</t>
+    <t>cumplirla（原形+宾格） | 第一人称(yo): cumplo | 第二人称(tú): cumples | 第三人称(él/ella/usted): cumple</t>
+  </si>
+  <si>
+    <t>他承诺就得履行，不管付出什么代价。</t>
+  </si>
+  <si>
+    <t>Él Una promesa hay que cumplirla, cueste lo que cueste.</t>
   </si>
   <si>
     <t>搭配：cumplir una promesa履行承诺；cumplir años过生日</t>
@@ -1455,13 +1446,13 @@
     <t>浇水</t>
   </si>
   <si>
-    <t>regar（原形）</t>
-  </si>
-  <si>
-    <t>我每天都学习，想着能收获个好分数</t>
-  </si>
-  <si>
-    <t>Estudio todos los días para cosechar buenas notas</t>
+    <t>regar（原形） | 第一人称(yo): rego | 第二人称(tú): regas | 第三人称(él/ella/usted): rega</t>
+  </si>
+  <si>
+    <t>我每天都学习，想着能收获个好分数。</t>
+  </si>
+  <si>
+    <t>Él Estudio todos los días para cosechar buenas notas.</t>
   </si>
   <si>
     <t>搭配：regar una planta给植物浇水；及物动词</t>
@@ -1473,13 +1464,10 @@
     <t>收获</t>
   </si>
   <si>
-    <t>cosechar（原形）</t>
-  </si>
-  <si>
-    <t>想着能收获个好分数</t>
-  </si>
-  <si>
-    <t>Estudio todos los días para cosechar buenas notas</t>
+    <t>cosechar（原形） | 第一人称(yo): cosecho | 第二人称(tú): cosechas | 第三人称(él/ella/usted): cosecha</t>
+  </si>
+  <si>
+    <t>他想着能收获个好分数。</t>
   </si>
   <si>
     <t>搭配：cosechar frutos收获果实；及物动词</t>
@@ -1491,13 +1479,13 @@
     <t>犁地</t>
   </si>
   <si>
-    <t>aro（一单）</t>
-  </si>
-  <si>
-    <t>有时候觉得自己在犁大海</t>
-  </si>
-  <si>
-    <t>A veces siento que aro el mar</t>
+    <t>aro（一单） | 第一人称(yo): aro | 第二人称(tú): aras | 第三人称(él/ella/usted): ara</t>
+  </si>
+  <si>
+    <t>他有时候觉得自己在犁大海。</t>
+  </si>
+  <si>
+    <t>Él A veces siento que aro el mar.</t>
   </si>
   <si>
     <t>搭配：arar la tierra犁地；及物动词</t>
@@ -1509,13 +1497,13 @@
     <t>开花</t>
   </si>
   <si>
-    <t>florecen（三复）</t>
-  </si>
-  <si>
-    <t>春天植物都开花了</t>
-  </si>
-  <si>
-    <t>Las plantas florecen en primavera</t>
+    <t>florecen（三复） | 第一人称(yo): floreco | 第二人称(tú): floreces | 第三人称(él/ella/usted): florece</t>
+  </si>
+  <si>
+    <t>他春天植物都开花了。</t>
+  </si>
+  <si>
+    <t>Las plantas florecen en primavera.</t>
   </si>
   <si>
     <t>不及物动词；搭配：florecer en primavera春天开花</t>
@@ -1527,13 +1515,13 @@
     <t>生长</t>
   </si>
   <si>
-    <t>crece（三单）</t>
-  </si>
-  <si>
-    <t>花园里的草长得很快</t>
-  </si>
-  <si>
-    <t>El pasto del jardin crece muy rapido</t>
+    <t>crece（三单） | 第一人称(yo): creco | 第二人称(tú): creces | 第三人称(él/ella/usted): crece</t>
+  </si>
+  <si>
+    <t>他花园里的草长得很快。</t>
+  </si>
+  <si>
+    <t>El pasto del jardin crece muy rapido.</t>
   </si>
   <si>
     <t>不及物动词；搭配：crecer rápido长得快</t>
@@ -1545,13 +1533,13 @@
     <t>修剪</t>
   </si>
   <si>
-    <t>podar（原形）</t>
-  </si>
-  <si>
-    <t>我每两个月就得修剪一次树枝</t>
-  </si>
-  <si>
-    <t>Tengo que podar los arboles cada dos meses</t>
+    <t>podar（原形） | 第一人称(yo): podo | 第二人称(tú): podas | 第三人称(él/ella/usted): poda</t>
+  </si>
+  <si>
+    <t>我每两个月就得修剪一次树枝。</t>
+  </si>
+  <si>
+    <t>Él Tengo que podar los arboles cada dos meses.</t>
   </si>
   <si>
     <t>搭配：podar los árboles修剪树枝；及物动词</t>
@@ -1563,13 +1551,13 @@
     <t>天亮/日出</t>
   </si>
   <si>
-    <t>amanecer（原形）</t>
-  </si>
-  <si>
-    <t>如果你等到天亮，它们就消失了</t>
-  </si>
-  <si>
-    <t>Si esperas hasta que amanece, desaparecen</t>
+    <t>amanecer（原形） | 第一人称(yo): amaneco | 第二人称(tú): amaneces | 第三人称(él/ella/usted): amanece</t>
+  </si>
+  <si>
+    <t>如果你等到天亮，它们就消失了。</t>
+  </si>
+  <si>
+    <t>Él Si esperas hasta que amanece, desaparecen.</t>
   </si>
   <si>
     <t>不及物动词；无人称：amanece天亮了</t>
@@ -1581,13 +1569,13 @@
     <t>天黑/日落</t>
   </si>
   <si>
-    <t>anochece（三单）</t>
-  </si>
-  <si>
-    <t>天黑的时候星星闪耀得更亮</t>
-  </si>
-  <si>
-    <t>Las estrellas brillan mas cuando anochece</t>
+    <t>anochece（三单） | 第一人称(yo): anocheco | 第二人称(tú): anocheces | 第三人称(él/ella/usted): anochece</t>
+  </si>
+  <si>
+    <t>他天黑的时候星星闪耀得更亮。</t>
+  </si>
+  <si>
+    <t>Las estrellas brillan mas cuando anochece.</t>
   </si>
   <si>
     <t>不及物动词；无人称：anochece天黑了</t>
@@ -1599,13 +1587,7 @@
     <t>闪耀</t>
   </si>
   <si>
-    <t>brillan（三复）</t>
-  </si>
-  <si>
-    <t>天黑的时候星星闪耀得更亮</t>
-  </si>
-  <si>
-    <t>Las estrellas brillan mas cuando anochece</t>
+    <t>brillan（三复） | 第一人称(yo): brillo | 第二人称(tú): brillas | 第三人称(él/ella/usted): brilla</t>
   </si>
   <si>
     <t>不及物动词；搭配：brillar con luz propia自身发光</t>
@@ -1617,13 +1599,13 @@
     <t>下冰雹</t>
   </si>
   <si>
-    <t>granizar（原形）</t>
-  </si>
-  <si>
-    <t>小时候，下冰雹让我很惊奇</t>
-  </si>
-  <si>
-    <t>De chico, granizar me sorprendia un montón</t>
+    <t>granizar（原形） | 第一人称(yo): granizo | 第二人称(tú): granizas | 第三人称(él/ella/usted): graniza</t>
+  </si>
+  <si>
+    <t>小时候，下冰雹让我很惊奇。</t>
+  </si>
+  <si>
+    <t>Él De chico, granizar me sorprendia un montón.</t>
   </si>
   <si>
     <t>不及物动词；无人称：graniza下冰雹</t>
@@ -1635,13 +1617,13 @@
     <t>闪电(闪出光)</t>
   </si>
   <si>
-    <t>destellar（原形）</t>
-  </si>
-  <si>
-    <t>闪出光让我觉得很神奇</t>
-  </si>
-  <si>
-    <t>Destellar me parecía magico</t>
+    <t>destellar（原形） | 第一人称(yo): destello | 第二人称(tú): destellas | 第三人称(él/ella/usted): destella</t>
+  </si>
+  <si>
+    <t>闪出光让我觉得很神奇。</t>
+  </si>
+  <si>
+    <t>Él Destellar me parecía magico.</t>
   </si>
   <si>
     <t>不及物动词；无人称：destella闪电</t>
@@ -1653,13 +1635,13 @@
     <t>打雷</t>
   </si>
   <si>
-    <t>tronar（原形）</t>
-  </si>
-  <si>
-    <t>而打雷会让我害怕</t>
-  </si>
-  <si>
-    <t>Y tronar me asustaba</t>
+    <t>tronar（原形） | 第一人称(yo): trono | 第二人称(tú): tronas | 第三人称(él/ella/usted): trona</t>
+  </si>
+  <si>
+    <t>而打雷会让我害怕。</t>
+  </si>
+  <si>
+    <t>Él Y tronar me asustaba.</t>
   </si>
   <si>
     <t>不及物动词；无人称：trona打雷</t>
@@ -1671,13 +1653,13 @@
     <t>减少</t>
   </si>
   <si>
-    <t>disminuir（原形）</t>
-  </si>
-  <si>
-    <t>为了减少焦虑，我深呼吸</t>
-  </si>
-  <si>
-    <t>Para disminuir la ansiedad, respiro hondo</t>
+    <t>disminuir（原形） | 第一人称(yo): disminuo | 第二人称(tú): disminues | 第三人称(él/ella/usted): disminue</t>
+  </si>
+  <si>
+    <t>为了减少焦虑，我深呼吸。</t>
+  </si>
+  <si>
+    <t>Él Para disminuir la ansiedad, respiro hondo.</t>
   </si>
   <si>
     <t>-uir变位动词；搭配：disminuir el riesgo减少风险</t>
@@ -1689,13 +1671,13 @@
     <t>加速</t>
   </si>
   <si>
-    <t>acelera（三单）</t>
-  </si>
-  <si>
-    <t>音乐会加速或者减缓我的心跳</t>
-  </si>
-  <si>
-    <t>La música acelera mi corazón o lo frena</t>
+    <t>acelera（三单） | 第一人称(yo): acelero | 第二人称(tú): aceleras | 第三人称(él/ella/usted): acelera</t>
+  </si>
+  <si>
+    <t>音乐会加速或者减缓我的心跳。</t>
+  </si>
+  <si>
+    <t>La música acelera mi corazón o lo frena.</t>
   </si>
   <si>
     <t>搭配：acelerar el paso加速步伐；及物动词</t>
@@ -1707,13 +1689,7 @@
     <t>刹车/阻止</t>
   </si>
   <si>
-    <t>frena（三单）</t>
-  </si>
-  <si>
-    <t>音乐会加速或者减缓我的心跳</t>
-  </si>
-  <si>
-    <t>La música acelera mi corazón o lo frena</t>
+    <t>frena（三单） | 第一人称(yo): freno | 第二人称(tú): frenas | 第三人称(él/ella/usted): frena</t>
   </si>
   <si>
     <t>搭配：frenar el coche刹车；及物动词</t>
@@ -1725,13 +1701,13 @@
     <t>融合</t>
   </si>
   <si>
-    <t>fusiona（三单）</t>
-  </si>
-  <si>
-    <t>这位大厨融合了不同国家的口味</t>
-  </si>
-  <si>
-    <t>La chef fusiona sabores de diferentes paises</t>
+    <t>fusiona（三单） | 第一人称(yo): fusiono | 第二人称(tú): fusionas | 第三人称(él/ella/usted): fusiona</t>
+  </si>
+  <si>
+    <t>他这位大厨融合了不同国家的口味。</t>
+  </si>
+  <si>
+    <t>La chef fusiona sabores de diferentes paises.</t>
   </si>
   <si>
     <t>搭配：fusionar sabores融合口味；及物动词</t>
@@ -1743,13 +1719,13 @@
     <t>转变</t>
   </si>
   <si>
-    <t>transforma（三单）</t>
-  </si>
-  <si>
-    <t>她把简单的食材转变成令人惊叹的菜肴</t>
-  </si>
-  <si>
-    <t>Transforma ingredientes simples en platos increibles</t>
+    <t>transforma（三单） | 第一人称(yo): transformo | 第二人称(tú): transformas | 第三人称(él/ella/usted): transforma</t>
+  </si>
+  <si>
+    <t>她把简单的食材转变成令人惊叹的菜肴。</t>
+  </si>
+  <si>
+    <t>Él Transforma ingredientes simples en platos increibles.</t>
   </si>
   <si>
     <t>搭配：transformar A en B把A转变为B；及物动词</t>
@@ -1761,13 +1737,13 @@
     <t>增加</t>
   </si>
   <si>
-    <t>aumenta（三单）</t>
-  </si>
-  <si>
-    <t>这增加了她餐厅的名气</t>
-  </si>
-  <si>
-    <t>Eso aumenta la fama de su restaurante</t>
+    <t>aumenta（三单） | 第一人称(yo): aumento | 第二人称(tú): aumentas | 第三人称(él/ella/usted): aumenta</t>
+  </si>
+  <si>
+    <t>这增加了她餐厅的名气。</t>
+  </si>
+  <si>
+    <t>Él Eso aumenta la fama de su restaurante.</t>
   </si>
   <si>
     <t>搭配：aumentar el precio提高价格；及物/不及物</t>
@@ -1779,13 +1755,13 @@
     <t>排除</t>
   </si>
   <si>
-    <t>excluir（原形）</t>
-  </si>
-  <si>
-    <t>在工作中，不应该排除新想法</t>
-  </si>
-  <si>
-    <t>En el trabajo, no hay que excluir las ideas nuevas</t>
+    <t>excluir（原形） | 第一人称(yo): excluo | 第二人称(tú): exclues | 第三人称(él/ella/usted): exclue</t>
+  </si>
+  <si>
+    <t>他在工作中，不应该排除新想法。</t>
+  </si>
+  <si>
+    <t>Él En el trabajo, no hay que excluir las ideas nuevas.</t>
   </si>
   <si>
     <t>搭配：excluir algo排除某物；及物动词</t>
@@ -1797,13 +1773,13 @@
     <t>分离</t>
   </si>
   <si>
-    <t>separan（三复）</t>
-  </si>
-  <si>
-    <t>偏见可能会分离同事之间的关系</t>
-  </si>
-  <si>
-    <t>Los prejuicios pueden separar a los companeros</t>
+    <t>separan（三复） | 第一人称(yo): separo | 第二人称(tú): separas | 第三人称(él/ella/usted): separa</t>
+  </si>
+  <si>
+    <t>他偏见可能会分离同事之间的关系。</t>
+  </si>
+  <si>
+    <t>Los prejuicios pueden separar a los companeros.</t>
   </si>
   <si>
     <t>搭配：separar A de B把A和B分离；及物动词</t>
@@ -1815,13 +1791,13 @@
     <t>联合</t>
   </si>
   <si>
-    <t>une（三单）</t>
-  </si>
-  <si>
-    <t>一个成功的项目会联合各种不同的才华</t>
-  </si>
-  <si>
-    <t>Un proyecto exitoso une talentos diversos</t>
+    <t>une（三单） | 第一人称(yo): uno | 第二人称(tú): unes | 第三人称(él/ella/usted): une</t>
+  </si>
+  <si>
+    <t>他一个成功的项目会联合各种不同的才华。</t>
+  </si>
+  <si>
+    <t>Él Un proyecto exitoso une talentos diversos.</t>
   </si>
   <si>
     <t>变位特殊：yo uno；搭配：unir A y B联合A和B</t>
@@ -1833,13 +1809,13 @@
     <t>嫉妒</t>
   </si>
   <si>
-    <t>envidia（三单）</t>
-  </si>
-  <si>
-    <t>真正的友谊不会嫉妒对方的成就</t>
-  </si>
-  <si>
-    <t>Una amistad verdadera no envidia los logros del otro</t>
+    <t>envidia（三单） | 第一人称(yo): envidio | 第二人称(tú): envidias | 第三人称(él/ella/usted): envidia</t>
+  </si>
+  <si>
+    <t>他真正的友谊不会嫉妒对方的成就。</t>
+  </si>
+  <si>
+    <t>Él Una amistad verdadera no envidia los logros del otro.</t>
   </si>
   <si>
     <t>搭配：envidiar a alguien嫉妒某人；需加前置词a</t>
@@ -1851,13 +1827,13 @@
     <t>背叛</t>
   </si>
   <si>
-    <t>traiciona（三单）</t>
-  </si>
-  <si>
-    <t>也不会背叛信任</t>
-  </si>
-  <si>
-    <t>Tampoco traiciona la confianza</t>
+    <t>traiciona（三单） | 第一人称(yo): traiciono | 第二人称(tú): traicionas | 第三人称(él/ella/usted): traiciona</t>
+  </si>
+  <si>
+    <t>他也不会背叛信任。</t>
+  </si>
+  <si>
+    <t>Él Tampoco traiciona la confianza.</t>
   </si>
   <si>
     <t>搭配：traicionar a alguien背叛某人；需加前置词a</t>
@@ -1869,13 +1845,13 @@
     <t>包括</t>
   </si>
   <si>
-    <t>incluye（三单）</t>
-  </si>
-  <si>
-    <t>它包含在困难的时候陪伴</t>
-  </si>
-  <si>
-    <t>Incluye estar presente en las malas</t>
+    <t>incluye（三单） | 第一人称(yo): incluo | 第二人称(tú): inclues | 第三人称(él/ella/usted): inclue</t>
+  </si>
+  <si>
+    <t>它包含在困难的时候陪伴。</t>
+  </si>
+  <si>
+    <t>Él Incluye estar presente en las malas.</t>
   </si>
   <si>
     <t>搭配：incluir algo包括某物；及物动词</t>
@@ -1887,13 +1863,13 @@
     <t>批评</t>
   </si>
   <si>
-    <t>critican（三复）</t>
-  </si>
-  <si>
-    <t>在网上，什么他们都能批评一顿</t>
-  </si>
-  <si>
-    <t>En internet critican todo sin saber</t>
+    <t>critican（三复） | 第一人称(yo): critico | 第二人称(tú): criticas | 第三人称(él/ella/usted): critica</t>
+  </si>
+  <si>
+    <t>在网上，什么他们都能批评一顿。</t>
+  </si>
+  <si>
+    <t>Él En internet critican todo sin saber.</t>
   </si>
   <si>
     <t>搭配：criticar algo批评某物；及物动词</t>
@@ -1905,13 +1881,13 @@
     <t>赞扬</t>
   </si>
   <si>
-    <t>alaban（三复）</t>
-  </si>
-  <si>
-    <t>做对了的时候很少有人赞扬</t>
-  </si>
-  <si>
-    <t>Pocos alaban cuando algo está bien</t>
+    <t>alaban（三复） | 第一人称(yo): alabo | 第二人称(tú): alabas | 第三人称(él/ella/usted): alaba</t>
+  </si>
+  <si>
+    <t>他做对了的时候很少有人赞扬。</t>
+  </si>
+  <si>
+    <t>Él Pocos alaban cuando algo está bien.</t>
   </si>
   <si>
     <t>搭配：alabar a alguien赞扬某人；需加前置词a</t>
@@ -1923,13 +1899,13 @@
     <t>钦佩</t>
   </si>
   <si>
-    <t>admiro（一单）</t>
-  </si>
-  <si>
-    <t>我钦佩那些即使观点不同也能好好评论的人</t>
-  </si>
-  <si>
-    <t>Yo admiro a los que comentan con respeto</t>
+    <t>admiro（一单） | 第一人称(yo): admiro | 第二人称(tú): admiras | 第三人称(él/ella/usted): admira</t>
+  </si>
+  <si>
+    <t>我钦佩那些即使观点不同也能好好评论的人。</t>
+  </si>
+  <si>
+    <t>Él Yo admiro a los que comentan con respeto.</t>
   </si>
   <si>
     <t>搭配：admirar a alguien钦佩某人；需加前置词a</t>
@@ -1941,13 +1917,13 @@
     <t>合作</t>
   </si>
   <si>
-    <t>cooperamos（一单复）</t>
-  </si>
-  <si>
-    <t>不配合就完不成</t>
-  </si>
-  <si>
-    <t>Si no cooperamos, no lo terminamos</t>
+    <t>cooperamos（一单复） | 第一人称(yo): coopero | 第二人称(tú): cooperas | 第三人称(él/ella/usted): coopera</t>
+  </si>
+  <si>
+    <t>他不配合就完不成。</t>
+  </si>
+  <si>
+    <t>Él Si no cooperamos, no lo terminamos.</t>
   </si>
   <si>
     <t>搭配：cooperar con alguien和某人合作；需加前置词con</t>
@@ -1959,13 +1935,13 @@
     <t>打招呼</t>
   </si>
   <si>
-    <t>saludo（一单）</t>
-  </si>
-  <si>
-    <t>每天早上我跟同学打招呼</t>
-  </si>
-  <si>
-    <t>Cada manana saludo a mis companeros</t>
+    <t>saludo（一单） | 第一人称(yo): saludo | 第二人称(tú): saludas | 第三人称(él/ella/usted): saluda</t>
+  </si>
+  <si>
+    <t>每天早上我跟同学打招呼。</t>
+  </si>
+  <si>
+    <t>Él Cada manana saludo a mis companeros.</t>
   </si>
   <si>
     <t>搭配：saludar a alguien向某人打招呼；需加前置词a</t>
@@ -1977,13 +1953,13 @@
     <t>告别/解雇</t>
   </si>
   <si>
-    <t>despedimos（一单复）</t>
-  </si>
-  <si>
-    <t>年底，送别离开的同学时会拍张照</t>
-  </si>
-  <si>
-    <t>Al final del ano, despedimos a los que se van con una foto</t>
+    <t>despedimos（一单复） | 第一人称(yo): despedo | 第二人称(tú): despedes | 第三人称(él/ella/usted): despede</t>
+  </si>
+  <si>
+    <t>他年底，送别离开的同学时会拍张照。</t>
+  </si>
+  <si>
+    <t>Él Al final del ano, despedimos a los que se van con una foto.</t>
   </si>
   <si>
     <t>搭配：despedir a someone送别/解雇某人；需加前置词a</t>
@@ -1995,13 +1971,13 @@
     <t>存储</t>
   </si>
   <si>
-    <t>almacena（三单）</t>
-  </si>
-  <si>
-    <t>服务器里存着所有的合同</t>
-  </si>
-  <si>
-    <t>EI servidor almacena todos los contratos</t>
+    <t>almacena（三单） | 第一人称(yo): almaceno | 第二人称(tú): almacenas | 第三人称(él/ella/usted): almacena</t>
+  </si>
+  <si>
+    <t>他服务器里存着所有的合同。</t>
+  </si>
+  <si>
+    <t>El servidor almacena todos los contratos.</t>
   </si>
   <si>
     <t>搭配：almacenar datos存储数据；及物动词</t>
@@ -2013,13 +1989,13 @@
     <t>处理</t>
   </si>
   <si>
-    <t>procesa（三单）</t>
-  </si>
-  <si>
-    <t>律师会过一遍，查找问题</t>
-  </si>
-  <si>
-    <t>EI abogado los procesa para encontrar errores</t>
+    <t>procesa（三单） | 第一人称(yo): proceso | 第二人称(tú): procesas | 第三人称(él/ella/usted): procesa</t>
+  </si>
+  <si>
+    <t>他律师会过一遍，查找问题。</t>
+  </si>
+  <si>
+    <t>El abogado los procesa para encontrar errores.</t>
   </si>
   <si>
     <t>搭配：procesar información处理信息；及物动词</t>
@@ -2031,13 +2007,13 @@
     <t>执行/运行</t>
   </si>
   <si>
-    <t>ejecuta（三单）</t>
-  </si>
-  <si>
-    <t>没问题的话，老板就签字</t>
-  </si>
-  <si>
-    <t>Si está todo bien, el jefe ejecuta la firma</t>
+    <t>ejecuta（三单） | 第一人称(yo): ejecuto | 第二人称(tú): ejecutas | 第三人称(él/ella/usted): ejecuta</t>
+  </si>
+  <si>
+    <t>他没问题的话，老板就签字。</t>
+  </si>
+  <si>
+    <t>Él Si está todo bien, el jefe ejecuta la firma.</t>
   </si>
   <si>
     <t>搭配：ejecutar un plan执行计划；ejecutar un programa运行程序</t>
@@ -2049,13 +2025,13 @@
     <t>编程</t>
   </si>
   <si>
-    <t>programan（三复）</t>
-  </si>
-  <si>
-    <t>工程师们编程了一个会打扫屋子的机器人</t>
-  </si>
-  <si>
-    <t>Los ingenieros programan un robot que limpia la casa</t>
+    <t>programan（三复） | 第一人称(yo): programo | 第二人称(tú): programas | 第三人称(él/ella/usted): programa</t>
+  </si>
+  <si>
+    <t>他工程师们编程了一个会打扫屋子的机器人。</t>
+  </si>
+  <si>
+    <t>Los ingenieros programan un robot que limpia la casa.</t>
   </si>
   <si>
     <t>搭配：programar un robot给机器人编程；及物动词</t>
@@ -2067,13 +2043,13 @@
     <t>编码</t>
   </si>
   <si>
-    <t>codifican（三复）</t>
-  </si>
-  <si>
-    <t>他们精准编码每一个动作</t>
-  </si>
-  <si>
-    <t>Codifican cada movimiento con precisión</t>
+    <t>codifican（三复） | 第一人称(yo): codifico | 第二人称(tú): codificas | 第三人称(él/ella/usted): codifica</t>
+  </si>
+  <si>
+    <t>他们精准编码每一个动作。</t>
+  </si>
+  <si>
+    <t>Él Codifican cada movimiento con precisión.</t>
   </si>
   <si>
     <t>搭配：codificar información编码信息；及物动词</t>
@@ -2085,13 +2061,13 @@
     <t>解码</t>
   </si>
   <si>
-    <t>decodifica（三单）</t>
-  </si>
-  <si>
-    <t>机器人解码指令并执行</t>
-  </si>
-  <si>
-    <t>El robot decodifica las órdenes y las ejecuta</t>
+    <t>decodifica（三单） | 第一人称(yo): decodifico | 第二人称(tú): decodificas | 第三人称(él/ella/usted): decodifica</t>
+  </si>
+  <si>
+    <t>他机器人解码指令并执行。</t>
+  </si>
+  <si>
+    <t>El robot decodifica las órdenes y las ejecuta.</t>
   </si>
   <si>
     <t>搭配：decodificar información解码信息；及物动词</t>
@@ -2103,13 +2079,13 @@
     <t>扫描</t>
   </si>
   <si>
-    <t>escaneo（一单）</t>
-  </si>
-  <si>
-    <t>扔掉账单之前我先扫描一下</t>
-  </si>
-  <si>
-    <t>Escaneo las facturas antes de tirarlas</t>
+    <t>escaneo（一单） | 第一人称(yo): escaneo | 第二人称(tú): escaneas | 第三人称(él/ella/usted): escanea</t>
+  </si>
+  <si>
+    <t>扔掉账单之前我先扫描一下。</t>
+  </si>
+  <si>
+    <t>Él Escaneo las facturas antes de tirarlas.</t>
   </si>
   <si>
     <t>搭配：escanear un documento扫描文件；及物动词</t>
@@ -2121,13 +2097,13 @@
     <t>下载</t>
   </si>
   <si>
-    <t>descargo（一单）</t>
-  </si>
-  <si>
-    <t>有需要的话，我随时下载</t>
-  </si>
-  <si>
-    <t>Si las necesito, las descargo desde donde esté</t>
+    <t>descargo（一单） | 第一人称(yo): descargo | 第二人称(tú): descargas | 第三人称(él/ella/usted): descarga</t>
+  </si>
+  <si>
+    <t>有需要的话，我随时下载。</t>
+  </si>
+  <si>
+    <t>Él Si las necesito, las descargo desde donde esté.</t>
   </si>
   <si>
     <t>搭配：descargar un archivo下载文件；及物动词</t>
@@ -2139,13 +2115,13 @@
     <t>上传/上升</t>
   </si>
   <si>
-    <t>subo（一单）</t>
-  </si>
-  <si>
-    <t>把文件上传到一个文件夹</t>
-  </si>
-  <si>
-    <t>Subo los archivos a una carpeta</t>
+    <t>subo（一单） | 第一人称(yo): subo | 第二人称(tú): subes | 第三人称(él/ella/usted): sube</t>
+  </si>
+  <si>
+    <t>他把文件上传到一个文件夹。</t>
+  </si>
+  <si>
+    <t>Él Subo los archivos a una carpeta.</t>
   </si>
   <si>
     <t>搭配：subir un archivo上传文件；subir a una place上升到某处</t>
@@ -2157,13 +2133,13 @@
     <t>录制/刻录</t>
   </si>
   <si>
-    <t>grabamos（一单复）</t>
-  </si>
-  <si>
-    <t>我们录了她唱生日歌的声音</t>
-  </si>
-  <si>
-    <t>Grabamos su voz cantando el feliz cumpleanos</t>
+    <t>grabamos（一单复） | 第一人称(yo): grabo | 第二人称(tú): grabas | 第三人称(él/ella/usted): graba</t>
+  </si>
+  <si>
+    <t>我们录了她唱生日歌的声音。</t>
+  </si>
+  <si>
+    <t>Él Grabamos su voz cantando el feliz cumpleanos.</t>
   </si>
   <si>
     <t>搭配：grabar un vídeo录制视频；grabar un disco刻录光盘</t>
@@ -2175,13 +2151,13 @@
     <t>拍摄</t>
   </si>
   <si>
-    <t>filmamos（一单复）</t>
-  </si>
-  <si>
-    <t>我们拍了奶奶的生日</t>
-  </si>
-  <si>
-    <t>Filmamos el cumpleanos de la abuela</t>
+    <t>filmamos（一单复） | 第一人称(yo): filmo | 第二人称(tú): filmas | 第三人称(él/ella/usted): filma</t>
+  </si>
+  <si>
+    <t>我们拍了奶奶的生日。</t>
+  </si>
+  <si>
+    <t>Él Filmamos el cumpleanos de la abuela.</t>
   </si>
   <si>
     <t>搭配：filmar una película拍摄电影；及物动词</t>
@@ -2193,13 +2169,13 @@
     <t>点击</t>
   </si>
   <si>
-    <t>clicamos（一单复）</t>
-  </si>
-  <si>
-    <t>现在我们每次想她，就点开那个视频</t>
-  </si>
-  <si>
-    <t>Ahora clicamos ese video cada vez que la extranamos</t>
+    <t>clicamos（一单复） | 第一人称(yo): clico | 第二人称(tú): clicas | 第三人称(él/ella/usted): clica</t>
+  </si>
+  <si>
+    <t>现在我们每次想她，就点开那个视频。</t>
+  </si>
+  <si>
+    <t>Él Ahora clicamos ese video cada vez que la extranamos.</t>
   </si>
   <si>
     <t>搭配：clicar el botón点击按钮；拉美西语常用，西班牙多用pulsar</t>
@@ -2218,16 +2194,16 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
       <family val="2"/>
     </font>
     <font>
@@ -2281,19 +2257,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2330,7 +2306,7 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 2" descr="DHmoHX">
+        <xdr:cNvPr id="2" name="Picture 2" descr="QelrTN">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
@@ -2658,11 +2634,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2C40E4F-5259-4915-8CE2-1E989CDE5D82}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26FBCC0C-EB52-4BAC-A923-B11B485A1EF8}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:F121"/>
+  <dimension ref="A1:F122"/>
   <sheetFormatPr defaultColWidth="8" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16" customWidth="1"/>
@@ -2693,2402 +2669,2422 @@
     </row>
     <row r="2" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>150</v>
+        <v>24</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>151</v>
+        <v>25</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>152</v>
+        <v>26</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>153</v>
+        <v>144</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>159</v>
+        <v>150</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>160</v>
+        <v>151</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>161</v>
+        <v>152</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>164</v>
+        <v>155</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>166</v>
+        <v>157</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>169</v>
+        <v>160</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>170</v>
+        <v>161</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>173</v>
+        <v>164</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>174</v>
+        <v>165</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>176</v>
+        <v>167</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>178</v>
+        <v>169</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>180</v>
+        <v>171</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>186</v>
+        <v>177</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>187</v>
+        <v>178</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>197</v>
+        <v>188</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>202</v>
+        <v>193</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>203</v>
+        <v>194</v>
       </c>
     </row>
     <row r="35" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>206</v>
+        <v>197</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>207</v>
+        <v>198</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>208</v>
+        <v>199</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>209</v>
+        <v>200</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>210</v>
+        <v>201</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>212</v>
+        <v>203</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>213</v>
+        <v>204</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>214</v>
+        <v>205</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>215</v>
+        <v>206</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
-        <v>216</v>
+        <v>207</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>217</v>
+        <v>208</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>218</v>
+        <v>209</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>219</v>
+        <v>210</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>220</v>
+        <v>211</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>221</v>
+        <v>212</v>
       </c>
     </row>
     <row r="38" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>222</v>
+        <v>213</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>223</v>
+        <v>214</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>227</v>
+        <v>218</v>
       </c>
     </row>
     <row r="39" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>229</v>
+        <v>220</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>231</v>
+        <v>222</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>232</v>
+        <v>223</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>233</v>
+        <v>224</v>
       </c>
     </row>
     <row r="40" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>234</v>
+        <v>225</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>235</v>
+        <v>226</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>236</v>
+        <v>227</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>237</v>
+        <v>228</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>238</v>
+        <v>229</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>239</v>
+        <v>230</v>
       </c>
     </row>
     <row r="41" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
-        <v>240</v>
+        <v>231</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>241</v>
+        <v>232</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>242</v>
+        <v>233</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>245</v>
+        <v>236</v>
       </c>
     </row>
     <row r="42" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>246</v>
+        <v>237</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>247</v>
+        <v>238</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>248</v>
+        <v>239</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>249</v>
+        <v>240</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>250</v>
+        <v>241</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>251</v>
+        <v>242</v>
       </c>
     </row>
     <row r="43" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
-        <v>252</v>
+        <v>243</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>253</v>
+        <v>244</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>254</v>
+        <v>245</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>255</v>
+        <v>246</v>
       </c>
       <c r="E43" s="5" t="s">
-        <v>256</v>
+        <v>247</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>257</v>
+        <v>248</v>
       </c>
     </row>
     <row r="44" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>258</v>
+        <v>249</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>259</v>
+        <v>250</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>261</v>
+        <v>252</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>262</v>
+        <v>253</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>263</v>
+        <v>254</v>
       </c>
     </row>
     <row r="45" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
-        <v>264</v>
+        <v>255</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>265</v>
+        <v>256</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>266</v>
+        <v>257</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>267</v>
+        <v>258</v>
       </c>
       <c r="E45" s="5" t="s">
-        <v>268</v>
+        <v>259</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>269</v>
+        <v>260</v>
       </c>
     </row>
     <row r="46" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>270</v>
+        <v>261</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>271</v>
+        <v>262</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>272</v>
+        <v>263</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>273</v>
+        <v>264</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>274</v>
+        <v>265</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>275</v>
+        <v>266</v>
       </c>
     </row>
     <row r="47" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
-        <v>276</v>
+        <v>267</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>277</v>
+        <v>268</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>278</v>
+        <v>269</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>279</v>
+        <v>270</v>
       </c>
       <c r="E47" s="5" t="s">
-        <v>280</v>
+        <v>271</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>281</v>
+        <v>272</v>
       </c>
     </row>
     <row r="48" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>282</v>
+        <v>273</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>283</v>
+        <v>274</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>284</v>
+        <v>275</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>285</v>
+        <v>276</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>286</v>
+        <v>277</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>287</v>
+        <v>278</v>
       </c>
     </row>
     <row r="49" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
-        <v>288</v>
+        <v>279</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>290</v>
+        <v>281</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>291</v>
+        <v>282</v>
       </c>
       <c r="E49" s="5" t="s">
-        <v>292</v>
+        <v>283</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
     </row>
     <row r="50" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>294</v>
+        <v>285</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>295</v>
+        <v>286</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>296</v>
+        <v>287</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>297</v>
+        <v>288</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>298</v>
+        <v>289</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>299</v>
+        <v>290</v>
       </c>
     </row>
     <row r="51" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
-        <v>300</v>
+        <v>291</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>301</v>
+        <v>292</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>303</v>
+        <v>294</v>
       </c>
       <c r="E51" s="5" t="s">
-        <v>304</v>
+        <v>295</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>305</v>
+        <v>296</v>
       </c>
     </row>
     <row r="52" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>306</v>
+        <v>297</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>307</v>
+        <v>298</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>308</v>
+        <v>299</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>309</v>
+        <v>300</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>310</v>
+        <v>301</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>311</v>
+        <v>302</v>
       </c>
     </row>
     <row r="53" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="s">
-        <v>312</v>
+        <v>303</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>313</v>
+        <v>304</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>314</v>
+        <v>305</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>315</v>
+        <v>306</v>
       </c>
       <c r="E53" s="5" t="s">
-        <v>316</v>
+        <v>307</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>317</v>
+        <v>308</v>
       </c>
     </row>
     <row r="54" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>318</v>
+        <v>309</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>319</v>
+        <v>310</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>320</v>
+        <v>311</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>321</v>
+        <v>312</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>322</v>
+        <v>313</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>323</v>
+        <v>314</v>
       </c>
     </row>
     <row r="55" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="4" t="s">
-        <v>324</v>
+        <v>315</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>325</v>
+        <v>316</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>326</v>
+        <v>317</v>
       </c>
       <c r="D55" s="5" t="s">
-        <v>327</v>
+        <v>318</v>
       </c>
       <c r="E55" s="5" t="s">
-        <v>328</v>
+        <v>319</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>329</v>
+        <v>320</v>
       </c>
     </row>
     <row r="56" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>330</v>
+        <v>321</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>331</v>
+        <v>322</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>332</v>
+        <v>323</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>333</v>
+        <v>324</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>334</v>
+        <v>325</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>335</v>
+        <v>326</v>
       </c>
     </row>
     <row r="57" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="4" t="s">
-        <v>336</v>
+        <v>327</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>337</v>
+        <v>328</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>338</v>
+        <v>329</v>
       </c>
       <c r="D57" s="5" t="s">
-        <v>339</v>
+        <v>330</v>
       </c>
       <c r="E57" s="5" t="s">
-        <v>340</v>
+        <v>331</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>341</v>
+        <v>332</v>
       </c>
     </row>
     <row r="58" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>342</v>
+        <v>333</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>343</v>
+        <v>334</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>345</v>
+        <v>336</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>346</v>
+        <v>337</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>347</v>
+        <v>338</v>
       </c>
     </row>
     <row r="59" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="4" t="s">
-        <v>348</v>
+        <v>339</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>349</v>
+        <v>340</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>350</v>
+        <v>341</v>
       </c>
       <c r="D59" s="5" t="s">
-        <v>351</v>
+        <v>342</v>
       </c>
       <c r="E59" s="5" t="s">
-        <v>352</v>
+        <v>343</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>353</v>
+        <v>344</v>
       </c>
     </row>
     <row r="60" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>354</v>
+        <v>345</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>355</v>
+        <v>346</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>356</v>
+        <v>347</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>357</v>
+        <v>348</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>358</v>
+        <v>349</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>359</v>
+        <v>350</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="4" t="s">
-        <v>360</v>
+        <v>351</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>361</v>
+        <v>352</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>362</v>
+        <v>353</v>
       </c>
       <c r="D61" s="5" t="s">
-        <v>363</v>
+        <v>354</v>
       </c>
       <c r="E61" s="5" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>365</v>
+        <v>356</v>
       </c>
     </row>
     <row r="62" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
-        <v>366</v>
+        <v>357</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>367</v>
+        <v>358</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>368</v>
+        <v>359</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>369</v>
+        <v>360</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>370</v>
+        <v>361</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>371</v>
+        <v>362</v>
       </c>
     </row>
     <row r="63" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="4" t="s">
-        <v>372</v>
+        <v>363</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>373</v>
+        <v>364</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>374</v>
+        <v>365</v>
       </c>
       <c r="D63" s="5" t="s">
-        <v>375</v>
+        <v>366</v>
       </c>
       <c r="E63" s="5" t="s">
-        <v>376</v>
+        <v>367</v>
       </c>
       <c r="F63" s="4" t="s">
-        <v>377</v>
+        <v>368</v>
       </c>
     </row>
     <row r="64" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
-        <v>378</v>
+        <v>369</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>379</v>
+        <v>370</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>380</v>
+        <v>371</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>381</v>
+        <v>372</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>382</v>
+        <v>373</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>383</v>
+        <v>374</v>
       </c>
     </row>
     <row r="65" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="4" t="s">
-        <v>384</v>
+        <v>375</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>385</v>
+        <v>376</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>386</v>
+        <v>377</v>
       </c>
       <c r="D65" s="5" t="s">
-        <v>387</v>
+        <v>378</v>
       </c>
       <c r="E65" s="5" t="s">
-        <v>388</v>
+        <v>379</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>389</v>
+        <v>380</v>
       </c>
     </row>
     <row r="66" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>390</v>
+        <v>381</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>391</v>
+        <v>382</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>392</v>
+        <v>383</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>393</v>
+        <v>384</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>394</v>
+        <v>385</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>395</v>
+        <v>386</v>
       </c>
     </row>
     <row r="67" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="4" t="s">
-        <v>396</v>
+        <v>387</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>397</v>
+        <v>388</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>398</v>
+        <v>389</v>
       </c>
       <c r="D67" s="5" t="s">
-        <v>399</v>
+        <v>390</v>
       </c>
       <c r="E67" s="5" t="s">
-        <v>400</v>
+        <v>391</v>
       </c>
       <c r="F67" s="4" t="s">
-        <v>401</v>
+        <v>392</v>
       </c>
     </row>
     <row r="68" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
-        <v>402</v>
+        <v>393</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>403</v>
+        <v>394</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>404</v>
+        <v>395</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>405</v>
+        <v>396</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>406</v>
+        <v>397</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>407</v>
+        <v>398</v>
       </c>
     </row>
     <row r="69" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="4" t="s">
-        <v>408</v>
+        <v>399</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>409</v>
+        <v>400</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>410</v>
+        <v>401</v>
       </c>
       <c r="D69" s="5" t="s">
-        <v>411</v>
+        <v>402</v>
       </c>
       <c r="E69" s="5" t="s">
-        <v>412</v>
+        <v>403</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>413</v>
+        <v>404</v>
       </c>
     </row>
     <row r="70" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
-        <v>414</v>
+        <v>405</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>415</v>
+        <v>406</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>416</v>
+        <v>407</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>417</v>
+        <v>408</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>418</v>
+        <v>409</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>419</v>
+        <v>410</v>
       </c>
     </row>
     <row r="71" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="4" t="s">
-        <v>420</v>
+        <v>411</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>421</v>
+        <v>412</v>
       </c>
       <c r="C71" s="5" t="s">
-        <v>422</v>
+        <v>413</v>
       </c>
       <c r="D71" s="5" t="s">
-        <v>423</v>
+        <v>414</v>
       </c>
       <c r="E71" s="5" t="s">
-        <v>424</v>
+        <v>415</v>
       </c>
       <c r="F71" s="4" t="s">
-        <v>425</v>
+        <v>416</v>
       </c>
     </row>
     <row r="72" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
-        <v>426</v>
+        <v>417</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>427</v>
+        <v>418</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>428</v>
+        <v>419</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>429</v>
+        <v>420</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>430</v>
+        <v>421</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>431</v>
+        <v>422</v>
       </c>
     </row>
     <row r="73" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="4" t="s">
-        <v>432</v>
+        <v>423</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>433</v>
+        <v>424</v>
       </c>
       <c r="C73" s="5" t="s">
-        <v>434</v>
+        <v>425</v>
       </c>
       <c r="D73" s="5" t="s">
-        <v>435</v>
+        <v>426</v>
       </c>
       <c r="E73" s="5" t="s">
-        <v>436</v>
+        <v>427</v>
       </c>
       <c r="F73" s="4" t="s">
-        <v>437</v>
+        <v>428</v>
       </c>
     </row>
     <row r="74" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
-        <v>438</v>
+        <v>429</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>439</v>
+        <v>430</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>440</v>
+        <v>431</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>441</v>
+        <v>432</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>442</v>
+        <v>433</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>443</v>
+        <v>434</v>
       </c>
     </row>
     <row r="75" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="4" t="s">
-        <v>444</v>
+        <v>435</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>445</v>
+        <v>436</v>
       </c>
       <c r="C75" s="5" t="s">
-        <v>446</v>
+        <v>437</v>
       </c>
       <c r="D75" s="5" t="s">
-        <v>447</v>
+        <v>438</v>
       </c>
       <c r="E75" s="5" t="s">
-        <v>448</v>
+        <v>439</v>
       </c>
       <c r="F75" s="4" t="s">
-        <v>449</v>
+        <v>440</v>
       </c>
     </row>
     <row r="76" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
-        <v>450</v>
+        <v>441</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>451</v>
+        <v>442</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>452</v>
+        <v>443</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>453</v>
+        <v>444</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>454</v>
+        <v>445</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>455</v>
+        <v>446</v>
       </c>
     </row>
     <row r="77" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="4" t="s">
-        <v>456</v>
+        <v>447</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>457</v>
+        <v>448</v>
       </c>
       <c r="C77" s="5" t="s">
-        <v>458</v>
+        <v>449</v>
       </c>
       <c r="D77" s="5" t="s">
-        <v>459</v>
+        <v>450</v>
       </c>
       <c r="E77" s="5" t="s">
-        <v>460</v>
+        <v>451</v>
       </c>
       <c r="F77" s="4" t="s">
-        <v>461</v>
+        <v>452</v>
       </c>
     </row>
     <row r="78" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
-        <v>462</v>
+        <v>453</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>463</v>
+        <v>454</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>464</v>
+        <v>455</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>465</v>
+        <v>456</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>466</v>
+        <v>457</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>467</v>
+        <v>458</v>
       </c>
     </row>
     <row r="79" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="4" t="s">
-        <v>468</v>
+        <v>459</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>469</v>
+        <v>460</v>
       </c>
       <c r="C79" s="5" t="s">
-        <v>470</v>
+        <v>461</v>
       </c>
       <c r="D79" s="5" t="s">
-        <v>471</v>
+        <v>462</v>
       </c>
       <c r="E79" s="5" t="s">
-        <v>472</v>
+        <v>463</v>
       </c>
       <c r="F79" s="4" t="s">
-        <v>473</v>
+        <v>464</v>
       </c>
     </row>
     <row r="80" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
-        <v>474</v>
+        <v>465</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>475</v>
+        <v>466</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>476</v>
+        <v>467</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>477</v>
+        <v>468</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>478</v>
+        <v>469</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>479</v>
+        <v>470</v>
       </c>
     </row>
     <row r="81" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="4" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>481</v>
+        <v>472</v>
       </c>
       <c r="C81" s="5" t="s">
-        <v>482</v>
+        <v>473</v>
       </c>
       <c r="D81" s="5" t="s">
-        <v>483</v>
+        <v>474</v>
       </c>
       <c r="E81" s="5" t="s">
-        <v>484</v>
+        <v>475</v>
       </c>
       <c r="F81" s="4" t="s">
-        <v>485</v>
+        <v>476</v>
       </c>
     </row>
     <row r="82" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
-        <v>486</v>
+        <v>477</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>487</v>
+        <v>478</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>488</v>
+        <v>479</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>489</v>
+        <v>480</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>490</v>
+        <v>475</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>491</v>
+        <v>481</v>
       </c>
     </row>
     <row r="83" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="4" t="s">
-        <v>492</v>
+        <v>482</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>493</v>
+        <v>483</v>
       </c>
       <c r="C83" s="5" t="s">
-        <v>494</v>
+        <v>484</v>
       </c>
       <c r="D83" s="5" t="s">
-        <v>495</v>
+        <v>485</v>
       </c>
       <c r="E83" s="5" t="s">
-        <v>496</v>
+        <v>486</v>
       </c>
       <c r="F83" s="4" t="s">
-        <v>497</v>
+        <v>487</v>
       </c>
     </row>
     <row r="84" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
-        <v>498</v>
+        <v>488</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>499</v>
+        <v>489</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>500</v>
+        <v>490</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>501</v>
+        <v>491</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>502</v>
+        <v>492</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>503</v>
+        <v>493</v>
       </c>
     </row>
     <row r="85" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="4" t="s">
-        <v>504</v>
+        <v>494</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>505</v>
+        <v>495</v>
       </c>
       <c r="C85" s="5" t="s">
-        <v>506</v>
+        <v>496</v>
       </c>
       <c r="D85" s="5" t="s">
-        <v>507</v>
+        <v>497</v>
       </c>
       <c r="E85" s="5" t="s">
-        <v>508</v>
+        <v>498</v>
       </c>
       <c r="F85" s="4" t="s">
-        <v>509</v>
+        <v>499</v>
       </c>
     </row>
     <row r="86" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
-        <v>510</v>
+        <v>500</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>511</v>
+        <v>501</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>512</v>
+        <v>502</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>513</v>
+        <v>503</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>514</v>
+        <v>504</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>515</v>
+        <v>505</v>
       </c>
     </row>
     <row r="87" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="4" t="s">
-        <v>516</v>
+        <v>506</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>517</v>
+        <v>507</v>
       </c>
       <c r="C87" s="5" t="s">
-        <v>518</v>
+        <v>508</v>
       </c>
       <c r="D87" s="5" t="s">
-        <v>519</v>
+        <v>509</v>
       </c>
       <c r="E87" s="5" t="s">
-        <v>520</v>
+        <v>510</v>
       </c>
       <c r="F87" s="4" t="s">
-        <v>521</v>
+        <v>511</v>
       </c>
     </row>
     <row r="88" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
-        <v>522</v>
+        <v>512</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>523</v>
+        <v>513</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>524</v>
+        <v>514</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>525</v>
+        <v>515</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>526</v>
+        <v>516</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>527</v>
+        <v>517</v>
       </c>
     </row>
     <row r="89" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="4" t="s">
-        <v>528</v>
+        <v>518</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>529</v>
+        <v>519</v>
       </c>
       <c r="C89" s="5" t="s">
-        <v>530</v>
+        <v>520</v>
       </c>
       <c r="D89" s="5" t="s">
-        <v>531</v>
+        <v>515</v>
       </c>
       <c r="E89" s="5" t="s">
-        <v>532</v>
+        <v>516</v>
       </c>
       <c r="F89" s="4" t="s">
-        <v>533</v>
+        <v>521</v>
       </c>
     </row>
     <row r="90" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
-        <v>534</v>
+        <v>522</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>535</v>
+        <v>523</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>536</v>
+        <v>524</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>537</v>
+        <v>525</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>538</v>
+        <v>526</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>539</v>
+        <v>527</v>
       </c>
     </row>
     <row r="91" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="4" t="s">
-        <v>540</v>
+        <v>528</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>541</v>
+        <v>529</v>
       </c>
       <c r="C91" s="5" t="s">
-        <v>542</v>
+        <v>530</v>
       </c>
       <c r="D91" s="5" t="s">
-        <v>543</v>
+        <v>531</v>
       </c>
       <c r="E91" s="5" t="s">
-        <v>544</v>
+        <v>532</v>
       </c>
       <c r="F91" s="4" t="s">
-        <v>545</v>
+        <v>533</v>
       </c>
     </row>
     <row r="92" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
-        <v>546</v>
+        <v>534</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>547</v>
+        <v>535</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>548</v>
+        <v>536</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>549</v>
+        <v>537</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>550</v>
+        <v>538</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>551</v>
+        <v>539</v>
       </c>
     </row>
     <row r="93" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="4" t="s">
-        <v>552</v>
+        <v>540</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>553</v>
+        <v>541</v>
       </c>
       <c r="C93" s="5" t="s">
-        <v>554</v>
+        <v>542</v>
       </c>
       <c r="D93" s="5" t="s">
-        <v>555</v>
+        <v>543</v>
       </c>
       <c r="E93" s="5" t="s">
-        <v>556</v>
+        <v>544</v>
       </c>
       <c r="F93" s="4" t="s">
-        <v>557</v>
+        <v>545</v>
       </c>
     </row>
     <row r="94" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
-        <v>558</v>
+        <v>546</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>559</v>
+        <v>547</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>560</v>
+        <v>548</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>561</v>
+        <v>549</v>
       </c>
       <c r="E94" s="3" t="s">
-        <v>562</v>
+        <v>550</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>563</v>
+        <v>551</v>
       </c>
     </row>
     <row r="95" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="4" t="s">
-        <v>564</v>
+        <v>552</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>565</v>
+        <v>553</v>
       </c>
       <c r="C95" s="5" t="s">
-        <v>566</v>
+        <v>554</v>
       </c>
       <c r="D95" s="5" t="s">
-        <v>567</v>
+        <v>549</v>
       </c>
       <c r="E95" s="5" t="s">
-        <v>568</v>
+        <v>550</v>
       </c>
       <c r="F95" s="4" t="s">
-        <v>569</v>
+        <v>555</v>
       </c>
     </row>
     <row r="96" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
-        <v>570</v>
+        <v>556</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>571</v>
+        <v>557</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>572</v>
+        <v>558</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>573</v>
+        <v>559</v>
       </c>
       <c r="E96" s="3" t="s">
-        <v>574</v>
+        <v>560</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>575</v>
+        <v>561</v>
       </c>
     </row>
     <row r="97" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="4" t="s">
-        <v>576</v>
+        <v>562</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>577</v>
+        <v>563</v>
       </c>
       <c r="C97" s="5" t="s">
-        <v>578</v>
+        <v>564</v>
       </c>
       <c r="D97" s="5" t="s">
-        <v>579</v>
+        <v>565</v>
       </c>
       <c r="E97" s="5" t="s">
-        <v>580</v>
+        <v>566</v>
       </c>
       <c r="F97" s="4" t="s">
-        <v>581</v>
+        <v>567</v>
       </c>
     </row>
     <row r="98" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
-        <v>582</v>
+        <v>568</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>583</v>
+        <v>569</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>584</v>
+        <v>570</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>585</v>
+        <v>571</v>
       </c>
       <c r="E98" s="3" t="s">
-        <v>586</v>
+        <v>572</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>587</v>
+        <v>573</v>
       </c>
     </row>
     <row r="99" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="4" t="s">
-        <v>588</v>
+        <v>574</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>589</v>
+        <v>575</v>
       </c>
       <c r="C99" s="5" t="s">
-        <v>590</v>
+        <v>576</v>
       </c>
       <c r="D99" s="5" t="s">
-        <v>591</v>
+        <v>577</v>
       </c>
       <c r="E99" s="5" t="s">
-        <v>592</v>
+        <v>578</v>
       </c>
       <c r="F99" s="4" t="s">
-        <v>593</v>
+        <v>579</v>
       </c>
     </row>
     <row r="100" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
-        <v>594</v>
+        <v>580</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>595</v>
+        <v>581</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>596</v>
+        <v>582</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>597</v>
+        <v>583</v>
       </c>
       <c r="E100" s="3" t="s">
-        <v>598</v>
+        <v>584</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>599</v>
+        <v>585</v>
       </c>
     </row>
     <row r="101" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="4" t="s">
-        <v>600</v>
+        <v>586</v>
       </c>
       <c r="B101" s="4" t="s">
-        <v>601</v>
+        <v>587</v>
       </c>
       <c r="C101" s="5" t="s">
-        <v>602</v>
+        <v>588</v>
       </c>
       <c r="D101" s="5" t="s">
-        <v>603</v>
+        <v>589</v>
       </c>
       <c r="E101" s="5" t="s">
-        <v>604</v>
+        <v>590</v>
       </c>
       <c r="F101" s="4" t="s">
-        <v>605</v>
+        <v>591</v>
       </c>
     </row>
     <row r="102" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
-        <v>606</v>
+        <v>592</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>607</v>
+        <v>593</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>608</v>
+        <v>594</v>
       </c>
       <c r="D102" s="3" t="s">
-        <v>609</v>
+        <v>595</v>
       </c>
       <c r="E102" s="3" t="s">
-        <v>610</v>
+        <v>596</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>611</v>
+        <v>597</v>
       </c>
     </row>
     <row r="103" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="4" t="s">
-        <v>612</v>
+        <v>598</v>
       </c>
       <c r="B103" s="4" t="s">
-        <v>613</v>
+        <v>599</v>
       </c>
       <c r="C103" s="5" t="s">
-        <v>614</v>
+        <v>600</v>
       </c>
       <c r="D103" s="5" t="s">
-        <v>615</v>
+        <v>601</v>
       </c>
       <c r="E103" s="5" t="s">
-        <v>616</v>
+        <v>602</v>
       </c>
       <c r="F103" s="4" t="s">
-        <v>617</v>
+        <v>603</v>
       </c>
     </row>
     <row r="104" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
-        <v>618</v>
+        <v>604</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>619</v>
+        <v>605</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>620</v>
+        <v>606</v>
       </c>
       <c r="D104" s="3" t="s">
-        <v>621</v>
+        <v>607</v>
       </c>
       <c r="E104" s="3" t="s">
-        <v>622</v>
+        <v>608</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>623</v>
+        <v>609</v>
       </c>
     </row>
     <row r="105" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="4" t="s">
-        <v>624</v>
+        <v>610</v>
       </c>
       <c r="B105" s="4" t="s">
-        <v>625</v>
+        <v>611</v>
       </c>
       <c r="C105" s="5" t="s">
-        <v>626</v>
+        <v>612</v>
       </c>
       <c r="D105" s="5" t="s">
-        <v>627</v>
+        <v>613</v>
       </c>
       <c r="E105" s="5" t="s">
-        <v>628</v>
+        <v>614</v>
       </c>
       <c r="F105" s="4" t="s">
-        <v>629</v>
+        <v>615</v>
       </c>
     </row>
     <row r="106" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
-        <v>630</v>
+        <v>616</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>631</v>
+        <v>617</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>632</v>
+        <v>618</v>
       </c>
       <c r="D106" s="3" t="s">
-        <v>633</v>
+        <v>619</v>
       </c>
       <c r="E106" s="3" t="s">
-        <v>634</v>
+        <v>620</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>635</v>
+        <v>621</v>
       </c>
     </row>
     <row r="107" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="4" t="s">
-        <v>636</v>
+        <v>622</v>
       </c>
       <c r="B107" s="4" t="s">
-        <v>637</v>
+        <v>623</v>
       </c>
       <c r="C107" s="5" t="s">
-        <v>638</v>
+        <v>624</v>
       </c>
       <c r="D107" s="5" t="s">
-        <v>639</v>
+        <v>625</v>
       </c>
       <c r="E107" s="5" t="s">
-        <v>640</v>
+        <v>626</v>
       </c>
       <c r="F107" s="4" t="s">
-        <v>641</v>
+        <v>627</v>
       </c>
     </row>
     <row r="108" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
-        <v>642</v>
+        <v>628</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>643</v>
+        <v>629</v>
       </c>
       <c r="C108" s="3" t="s">
-        <v>644</v>
+        <v>630</v>
       </c>
       <c r="D108" s="3" t="s">
-        <v>645</v>
+        <v>631</v>
       </c>
       <c r="E108" s="3" t="s">
-        <v>646</v>
+        <v>632</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>647</v>
+        <v>633</v>
       </c>
     </row>
     <row r="109" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="4" t="s">
-        <v>648</v>
+        <v>634</v>
       </c>
       <c r="B109" s="4" t="s">
-        <v>649</v>
+        <v>635</v>
       </c>
       <c r="C109" s="5" t="s">
-        <v>650</v>
+        <v>636</v>
       </c>
       <c r="D109" s="5" t="s">
-        <v>651</v>
+        <v>637</v>
       </c>
       <c r="E109" s="5" t="s">
-        <v>652</v>
+        <v>638</v>
       </c>
       <c r="F109" s="4" t="s">
-        <v>653</v>
+        <v>639</v>
       </c>
     </row>
     <row r="110" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="2" t="s">
-        <v>654</v>
+        <v>640</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>655</v>
+        <v>641</v>
       </c>
       <c r="C110" s="3" t="s">
-        <v>656</v>
+        <v>642</v>
       </c>
       <c r="D110" s="3" t="s">
-        <v>657</v>
+        <v>643</v>
       </c>
       <c r="E110" s="3" t="s">
-        <v>658</v>
+        <v>644</v>
       </c>
       <c r="F110" s="2" t="s">
-        <v>659</v>
+        <v>645</v>
       </c>
     </row>
     <row r="111" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="4" t="s">
-        <v>660</v>
+        <v>646</v>
       </c>
       <c r="B111" s="4" t="s">
-        <v>661</v>
+        <v>647</v>
       </c>
       <c r="C111" s="5" t="s">
-        <v>662</v>
+        <v>648</v>
       </c>
       <c r="D111" s="5" t="s">
-        <v>663</v>
+        <v>649</v>
       </c>
       <c r="E111" s="5" t="s">
-        <v>664</v>
+        <v>650</v>
       </c>
       <c r="F111" s="4" t="s">
-        <v>665</v>
+        <v>651</v>
       </c>
     </row>
     <row r="112" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
-        <v>666</v>
+        <v>652</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>667</v>
+        <v>653</v>
       </c>
       <c r="C112" s="3" t="s">
-        <v>668</v>
+        <v>654</v>
       </c>
       <c r="D112" s="3" t="s">
-        <v>669</v>
+        <v>655</v>
       </c>
       <c r="E112" s="3" t="s">
-        <v>670</v>
+        <v>656</v>
       </c>
       <c r="F112" s="2" t="s">
-        <v>671</v>
+        <v>657</v>
       </c>
     </row>
     <row r="113" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="4" t="s">
-        <v>672</v>
+        <v>658</v>
       </c>
       <c r="B113" s="4" t="s">
-        <v>673</v>
+        <v>659</v>
       </c>
       <c r="C113" s="5" t="s">
-        <v>674</v>
+        <v>660</v>
       </c>
       <c r="D113" s="5" t="s">
-        <v>675</v>
+        <v>661</v>
       </c>
       <c r="E113" s="5" t="s">
-        <v>676</v>
+        <v>662</v>
       </c>
       <c r="F113" s="4" t="s">
-        <v>677</v>
+        <v>663</v>
       </c>
     </row>
     <row r="114" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="2" t="s">
-        <v>678</v>
+        <v>664</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>679</v>
+        <v>665</v>
       </c>
       <c r="C114" s="3" t="s">
-        <v>680</v>
+        <v>666</v>
       </c>
       <c r="D114" s="3" t="s">
-        <v>681</v>
+        <v>667</v>
       </c>
       <c r="E114" s="3" t="s">
-        <v>682</v>
+        <v>668</v>
       </c>
       <c r="F114" s="2" t="s">
-        <v>683</v>
+        <v>669</v>
       </c>
     </row>
     <row r="115" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="4" t="s">
-        <v>684</v>
+        <v>670</v>
       </c>
       <c r="B115" s="4" t="s">
-        <v>685</v>
+        <v>671</v>
       </c>
       <c r="C115" s="5" t="s">
-        <v>686</v>
+        <v>672</v>
       </c>
       <c r="D115" s="5" t="s">
-        <v>687</v>
+        <v>673</v>
       </c>
       <c r="E115" s="5" t="s">
-        <v>688</v>
+        <v>674</v>
       </c>
       <c r="F115" s="4" t="s">
-        <v>689</v>
+        <v>675</v>
       </c>
     </row>
     <row r="116" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="2" t="s">
-        <v>690</v>
+        <v>676</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>691</v>
+        <v>677</v>
       </c>
       <c r="C116" s="3" t="s">
-        <v>692</v>
+        <v>678</v>
       </c>
       <c r="D116" s="3" t="s">
-        <v>693</v>
+        <v>679</v>
       </c>
       <c r="E116" s="3" t="s">
-        <v>694</v>
+        <v>680</v>
       </c>
       <c r="F116" s="2" t="s">
-        <v>695</v>
+        <v>681</v>
       </c>
     </row>
     <row r="117" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="4" t="s">
-        <v>696</v>
+        <v>682</v>
       </c>
       <c r="B117" s="4" t="s">
-        <v>697</v>
+        <v>683</v>
       </c>
       <c r="C117" s="5" t="s">
-        <v>698</v>
+        <v>684</v>
       </c>
       <c r="D117" s="5" t="s">
-        <v>699</v>
+        <v>685</v>
       </c>
       <c r="E117" s="5" t="s">
-        <v>700</v>
+        <v>686</v>
       </c>
       <c r="F117" s="4" t="s">
-        <v>701</v>
+        <v>687</v>
       </c>
     </row>
     <row r="118" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="2" t="s">
-        <v>702</v>
+        <v>688</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>703</v>
+        <v>689</v>
       </c>
       <c r="C118" s="3" t="s">
-        <v>704</v>
+        <v>690</v>
       </c>
       <c r="D118" s="3" t="s">
-        <v>705</v>
+        <v>691</v>
       </c>
       <c r="E118" s="3" t="s">
-        <v>706</v>
+        <v>692</v>
       </c>
       <c r="F118" s="2" t="s">
-        <v>707</v>
+        <v>693</v>
       </c>
     </row>
     <row r="119" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="4" t="s">
-        <v>708</v>
+        <v>694</v>
       </c>
       <c r="B119" s="4" t="s">
-        <v>709</v>
+        <v>695</v>
       </c>
       <c r="C119" s="5" t="s">
-        <v>710</v>
+        <v>696</v>
       </c>
       <c r="D119" s="5" t="s">
-        <v>711</v>
+        <v>697</v>
       </c>
       <c r="E119" s="5" t="s">
-        <v>712</v>
+        <v>698</v>
       </c>
       <c r="F119" s="4" t="s">
-        <v>713</v>
+        <v>699</v>
       </c>
     </row>
     <row r="120" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="2" t="s">
-        <v>714</v>
+        <v>700</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>715</v>
+        <v>701</v>
       </c>
       <c r="C120" s="3" t="s">
-        <v>716</v>
+        <v>702</v>
       </c>
       <c r="D120" s="3" t="s">
-        <v>717</v>
+        <v>703</v>
       </c>
       <c r="E120" s="3" t="s">
-        <v>718</v>
+        <v>704</v>
       </c>
       <c r="F120" s="2" t="s">
-        <v>719</v>
+        <v>705</v>
       </c>
     </row>
     <row r="121" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="4" t="s">
-        <v>720</v>
+        <v>706</v>
       </c>
       <c r="B121" s="4" t="s">
-        <v>721</v>
+        <v>707</v>
       </c>
       <c r="C121" s="5" t="s">
-        <v>722</v>
+        <v>708</v>
       </c>
       <c r="D121" s="5" t="s">
-        <v>723</v>
+        <v>709</v>
       </c>
       <c r="E121" s="5" t="s">
-        <v>724</v>
+        <v>710</v>
       </c>
       <c r="F121" s="4" t="s">
-        <v>725</v>
+        <v>711</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>712</v>
+      </c>
+      <c r="B122" t="s">
+        <v>713</v>
+      </c>
+      <c r="C122" t="s">
+        <v>714</v>
+      </c>
+      <c r="D122" t="s">
+        <v>715</v>
+      </c>
+      <c r="E122" t="s">
+        <v>716</v>
+      </c>
+      <c r="F122" t="s">
+        <v>717</v>
       </c>
     </row>
   </sheetData>
